--- a/AAII_Financials/Yearly/PAM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PAM_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="92">
   <si>
     <t>PAM</t>
   </si>
@@ -656,183 +656,195 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>44926</v>
+      </c>
+      <c r="E7" s="2">
         <v>44561</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44196</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>43830</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43465</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43100</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>42735</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42369</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42004</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>41639</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41274</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>40908</v>
       </c>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>623400</v>
+        <v>285800</v>
       </c>
       <c r="E8" s="3">
-        <v>330900</v>
+        <v>170700</v>
       </c>
       <c r="F8" s="3">
-        <v>278900</v>
+        <v>90600</v>
       </c>
       <c r="G8" s="3">
-        <v>233300</v>
+        <v>76300</v>
       </c>
       <c r="H8" s="3">
-        <v>353500</v>
+        <v>63900</v>
       </c>
       <c r="I8" s="3">
-        <v>108200</v>
+        <v>96800</v>
       </c>
       <c r="J8" s="3">
+        <v>29600</v>
+      </c>
+      <c r="K8" s="3">
         <v>30900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>61600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>65800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>110700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>136900</v>
       </c>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>392900</v>
+        <v>178400</v>
       </c>
       <c r="E9" s="3">
-        <v>203200</v>
+        <v>107900</v>
       </c>
       <c r="F9" s="3">
-        <v>168500</v>
+        <v>55900</v>
       </c>
       <c r="G9" s="3">
-        <v>134900</v>
+        <v>46300</v>
       </c>
       <c r="H9" s="3">
-        <v>253900</v>
+        <v>37000</v>
       </c>
       <c r="I9" s="3">
-        <v>76600</v>
+        <v>70700</v>
       </c>
       <c r="J9" s="3">
+        <v>21600</v>
+      </c>
+      <c r="K9" s="3">
         <v>29400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>59800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>69100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>220500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>257900</v>
       </c>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>230500</v>
+        <v>107400</v>
       </c>
       <c r="E10" s="3">
-        <v>127700</v>
+        <v>62800</v>
       </c>
       <c r="F10" s="3">
-        <v>110300</v>
+        <v>34700</v>
       </c>
       <c r="G10" s="3">
-        <v>98400</v>
+        <v>30100</v>
       </c>
       <c r="H10" s="3">
-        <v>99500</v>
+        <v>26800</v>
       </c>
       <c r="I10" s="3">
-        <v>31600</v>
+        <v>26000</v>
       </c>
       <c r="J10" s="3">
+        <v>8100</v>
+      </c>
+      <c r="K10" s="3">
         <v>1400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-3300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-109800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-120900</v>
       </c>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -848,31 +860,32 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>300</v>
-      </c>
-      <c r="E12" s="3">
         <v>100</v>
       </c>
+      <c r="E12" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="F12" s="3">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="G12" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="H12" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="I12" s="3">
-        <v>400</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
+        <v>100</v>
+      </c>
+      <c r="J12" s="3">
+        <v>100</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -886,9 +899,12 @@
       <c r="N12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O12" s="3"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="3"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -925,87 +941,96 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-      <c r="O13" s="3"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>3200</v>
+        <v>8000</v>
       </c>
       <c r="E14" s="3">
-        <v>47200</v>
+        <v>2700</v>
       </c>
       <c r="F14" s="3">
-        <v>22000</v>
+        <v>13500</v>
       </c>
       <c r="G14" s="3">
-        <v>-60200</v>
+        <v>6300</v>
       </c>
       <c r="H14" s="3">
-        <v>-48100</v>
+        <v>-15800</v>
       </c>
       <c r="I14" s="3">
-        <v>22200</v>
+        <v>-12300</v>
       </c>
       <c r="J14" s="3">
+        <v>6600</v>
+      </c>
+      <c r="K14" s="3">
         <v>1100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>34200</v>
       </c>
-      <c r="O14" s="3"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2200</v>
+        <v>900</v>
       </c>
       <c r="E15" s="3">
-        <v>1600</v>
+        <v>600</v>
       </c>
       <c r="F15" s="3">
-        <v>2000</v>
+        <v>400</v>
       </c>
       <c r="G15" s="3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="H15" s="3">
-        <v>1500</v>
+        <v>300</v>
       </c>
       <c r="I15" s="3">
+        <v>400</v>
+      </c>
+      <c r="J15" s="3">
+        <v>100</v>
+      </c>
+      <c r="K15" s="3">
+        <v>200</v>
+      </c>
+      <c r="L15" s="3">
+        <v>400</v>
+      </c>
+      <c r="M15" s="3">
+        <v>300</v>
+      </c>
+      <c r="N15" s="3">
         <v>500</v>
       </c>
-      <c r="J15" s="3">
-        <v>200</v>
-      </c>
-      <c r="K15" s="3">
-        <v>400</v>
-      </c>
-      <c r="L15" s="3">
-        <v>300</v>
-      </c>
-      <c r="M15" s="3">
-        <v>500</v>
-      </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>600</v>
       </c>
-      <c r="O15" s="3"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1018,86 +1043,93 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>380200</v>
+        <v>181400</v>
       </c>
       <c r="E17" s="3">
-        <v>252500</v>
+        <v>104000</v>
       </c>
       <c r="F17" s="3">
-        <v>182900</v>
+        <v>69100</v>
       </c>
       <c r="G17" s="3">
-        <v>67000</v>
+        <v>50100</v>
       </c>
       <c r="H17" s="3">
-        <v>244200</v>
+        <v>18400</v>
       </c>
       <c r="I17" s="3">
-        <v>99700</v>
+        <v>66900</v>
       </c>
       <c r="J17" s="3">
+        <v>27300</v>
+      </c>
+      <c r="K17" s="3">
         <v>15200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>52800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>44500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>122000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>144700</v>
       </c>
-      <c r="O17" s="3"/>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3"/>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>243200</v>
+        <v>104400</v>
       </c>
       <c r="E18" s="3">
-        <v>78400</v>
+        <v>66700</v>
       </c>
       <c r="F18" s="3">
-        <v>95900</v>
+        <v>21500</v>
       </c>
       <c r="G18" s="3">
-        <v>166200</v>
+        <v>26300</v>
       </c>
       <c r="H18" s="3">
-        <v>109200</v>
+        <v>45500</v>
       </c>
       <c r="I18" s="3">
-        <v>8500</v>
+        <v>29900</v>
       </c>
       <c r="J18" s="3">
+        <v>2300</v>
+      </c>
+      <c r="K18" s="3">
         <v>15700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>8800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>21300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-11300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-7800</v>
       </c>
-      <c r="O18" s="3"/>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3"/>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1113,203 +1145,219 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-22800</v>
+        <v>22900</v>
       </c>
       <c r="E20" s="3">
-        <v>25600</v>
+        <v>-6300</v>
       </c>
       <c r="F20" s="3">
-        <v>37400</v>
+        <v>7000</v>
       </c>
       <c r="G20" s="3">
-        <v>-131000</v>
+        <v>10200</v>
       </c>
       <c r="H20" s="3">
-        <v>-17600</v>
+        <v>-35900</v>
       </c>
       <c r="I20" s="3">
-        <v>-1800</v>
+        <v>-4800</v>
       </c>
       <c r="J20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="K20" s="3">
         <v>7500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>7100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-3000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>7000</v>
       </c>
-      <c r="O20" s="3"/>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3"/>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>305400</v>
+        <v>160000</v>
       </c>
       <c r="E21" s="3">
-        <v>166600</v>
+        <v>83600</v>
       </c>
       <c r="F21" s="3">
-        <v>193500</v>
+        <v>45600</v>
       </c>
       <c r="G21" s="3">
-        <v>73300</v>
+        <v>52900</v>
       </c>
       <c r="H21" s="3">
-        <v>125100</v>
+        <v>20100</v>
       </c>
       <c r="I21" s="3">
-        <v>16200</v>
+        <v>34200</v>
       </c>
       <c r="J21" s="3">
+        <v>4400</v>
+      </c>
+      <c r="K21" s="3">
         <v>26300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>20500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>22900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-7900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>9600</v>
       </c>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3"/>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>55700</v>
+        <v>27800</v>
       </c>
       <c r="E22" s="3">
-        <v>50200</v>
+        <v>15200</v>
       </c>
       <c r="F22" s="3">
-        <v>34300</v>
+        <v>13700</v>
       </c>
       <c r="G22" s="3">
-        <v>25600</v>
+        <v>9400</v>
       </c>
       <c r="H22" s="3">
-        <v>26300</v>
+        <v>7000</v>
       </c>
       <c r="I22" s="3">
-        <v>13300</v>
+        <v>7200</v>
       </c>
       <c r="J22" s="3">
+        <v>3600</v>
+      </c>
+      <c r="K22" s="3">
         <v>4000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>9600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>9300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>6500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>19200</v>
       </c>
-      <c r="O22" s="3"/>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3"/>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>164700</v>
+        <v>99500</v>
       </c>
       <c r="E23" s="3">
-        <v>53800</v>
+        <v>45200</v>
       </c>
       <c r="F23" s="3">
-        <v>99000</v>
+        <v>14700</v>
       </c>
       <c r="G23" s="3">
-        <v>9700</v>
+        <v>27100</v>
       </c>
       <c r="H23" s="3">
-        <v>65300</v>
+        <v>2600</v>
       </c>
       <c r="I23" s="3">
-        <v>-6600</v>
+        <v>17900</v>
       </c>
       <c r="J23" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="K23" s="3">
         <v>19100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>6200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>9000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-20600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-20100</v>
       </c>
-      <c r="O23" s="3"/>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3"/>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>31500</v>
+        <v>22900</v>
       </c>
       <c r="E24" s="3">
-        <v>13500</v>
+        <v>8600</v>
       </c>
       <c r="F24" s="3">
-        <v>-19500</v>
+        <v>3700</v>
       </c>
       <c r="G24" s="3">
-        <v>-5200</v>
+        <v>-5300</v>
       </c>
       <c r="H24" s="3">
-        <v>-4200</v>
+        <v>-1400</v>
       </c>
       <c r="I24" s="3">
-        <v>-5200</v>
+        <v>-1200</v>
       </c>
       <c r="J24" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="K24" s="3">
         <v>2500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-2200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-1000</v>
       </c>
-      <c r="O24" s="3"/>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3"/>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1346,87 +1394,96 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-      <c r="O25" s="3"/>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3"/>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>133200</v>
+        <v>76600</v>
       </c>
       <c r="E26" s="3">
-        <v>40400</v>
+        <v>36600</v>
       </c>
       <c r="F26" s="3">
-        <v>118500</v>
+        <v>11100</v>
       </c>
       <c r="G26" s="3">
-        <v>14900</v>
+        <v>32400</v>
       </c>
       <c r="H26" s="3">
-        <v>69600</v>
+        <v>4100</v>
       </c>
       <c r="I26" s="3">
-        <v>-1400</v>
+        <v>19000</v>
       </c>
       <c r="J26" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K26" s="3">
         <v>16600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>5300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>9200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-18400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-19100</v>
       </c>
-      <c r="O26" s="3"/>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3"/>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>147500</v>
+        <v>76500</v>
       </c>
       <c r="E27" s="3">
-        <v>77100</v>
+        <v>40500</v>
       </c>
       <c r="F27" s="3">
-        <v>91400</v>
+        <v>21100</v>
       </c>
       <c r="G27" s="3">
-        <v>4600</v>
+        <v>25000</v>
       </c>
       <c r="H27" s="3">
-        <v>54700</v>
+        <v>1300</v>
       </c>
       <c r="I27" s="3">
-        <v>-400</v>
+        <v>15000</v>
       </c>
       <c r="J27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K27" s="3">
         <v>13200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>7400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>5100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-11300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3300</v>
       </c>
-      <c r="O27" s="3"/>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3"/>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1463,48 +1520,54 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-      <c r="O28" s="3"/>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3"/>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>-30700</v>
+        <v>0</v>
       </c>
       <c r="E29" s="3">
-        <v>-212600</v>
+        <v>-8400</v>
       </c>
       <c r="F29" s="3">
-        <v>50900</v>
+        <v>-58200</v>
       </c>
       <c r="G29" s="3">
-        <v>31700</v>
+        <v>13900</v>
       </c>
       <c r="H29" s="3">
-        <v>-8200</v>
+        <v>8700</v>
       </c>
       <c r="I29" s="3">
-        <v>300</v>
-      </c>
-      <c r="J29" s="3" t="s">
+        <v>-2200</v>
+      </c>
+      <c r="J29" s="3">
+        <v>100</v>
+      </c>
+      <c r="K29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>-1600</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>500</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-2400</v>
       </c>
-      <c r="O29" s="3"/>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3"/>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1541,9 +1604,12 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-      <c r="O30" s="3"/>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1580,87 +1646,96 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-      <c r="O31" s="3"/>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3"/>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>22800</v>
+        <v>-22900</v>
       </c>
       <c r="E32" s="3">
-        <v>-25600</v>
+        <v>6300</v>
       </c>
       <c r="F32" s="3">
-        <v>-37400</v>
+        <v>-7000</v>
       </c>
       <c r="G32" s="3">
-        <v>131000</v>
+        <v>-10200</v>
       </c>
       <c r="H32" s="3">
-        <v>17600</v>
+        <v>35900</v>
       </c>
       <c r="I32" s="3">
-        <v>1800</v>
+        <v>4800</v>
       </c>
       <c r="J32" s="3">
+        <v>500</v>
+      </c>
+      <c r="K32" s="3">
         <v>-7500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-7100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>3000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-7000</v>
       </c>
-      <c r="O32" s="3"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3"/>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>116800</v>
+        <v>76500</v>
       </c>
       <c r="E33" s="3">
-        <v>-135500</v>
+        <v>32000</v>
       </c>
       <c r="F33" s="3">
-        <v>142300</v>
+        <v>-37100</v>
       </c>
       <c r="G33" s="3">
-        <v>36400</v>
+        <v>39000</v>
       </c>
       <c r="H33" s="3">
-        <v>46500</v>
+        <v>10000</v>
       </c>
       <c r="I33" s="3">
-        <v>0</v>
+        <v>12700</v>
       </c>
       <c r="J33" s="3">
+        <v>0</v>
+      </c>
+      <c r="K33" s="3">
         <v>13200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>7400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-10700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>900</v>
       </c>
-      <c r="O33" s="3"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1697,92 +1772,101 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-      <c r="O34" s="3"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3"/>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>116800</v>
+        <v>76500</v>
       </c>
       <c r="E35" s="3">
-        <v>-135500</v>
+        <v>32000</v>
       </c>
       <c r="F35" s="3">
-        <v>142300</v>
+        <v>-37100</v>
       </c>
       <c r="G35" s="3">
-        <v>36400</v>
+        <v>39000</v>
       </c>
       <c r="H35" s="3">
-        <v>46500</v>
+        <v>10000</v>
       </c>
       <c r="I35" s="3">
-        <v>0</v>
+        <v>12700</v>
       </c>
       <c r="J35" s="3">
+        <v>0</v>
+      </c>
+      <c r="K35" s="3">
         <v>13200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>7400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-10700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>900</v>
       </c>
-      <c r="O35" s="3"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>44926</v>
+      </c>
+      <c r="E38" s="2">
         <v>44561</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44196</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>43830</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43465</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43100</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>42735</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42369</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42004</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>41639</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41274</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>40908</v>
       </c>
-      <c r="O38" s="2"/>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1798,8 +1882,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1815,359 +1900,387 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>48600</v>
+        <v>22100</v>
       </c>
       <c r="E41" s="3">
-        <v>51300</v>
+        <v>13300</v>
       </c>
       <c r="F41" s="3">
-        <v>58200</v>
+        <v>14000</v>
       </c>
       <c r="G41" s="3">
-        <v>43500</v>
+        <v>15900</v>
       </c>
       <c r="H41" s="3">
-        <v>5100</v>
+        <v>11900</v>
       </c>
       <c r="I41" s="3">
-        <v>6100</v>
+        <v>1400</v>
       </c>
       <c r="J41" s="3">
+        <v>1700</v>
+      </c>
+      <c r="K41" s="3">
         <v>4500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>9000</v>
       </c>
-      <c r="O41" s="3"/>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>205000</v>
+        <v>124200</v>
       </c>
       <c r="E42" s="3">
-        <v>126900</v>
+        <v>56100</v>
       </c>
       <c r="F42" s="3">
-        <v>108100</v>
+        <v>34700</v>
       </c>
       <c r="G42" s="3">
-        <v>79300</v>
+        <v>29600</v>
       </c>
       <c r="H42" s="3">
-        <v>93200</v>
+        <v>21700</v>
       </c>
       <c r="I42" s="3">
-        <v>18100</v>
+        <v>25500</v>
       </c>
       <c r="J42" s="3">
+        <v>5000</v>
+      </c>
+      <c r="K42" s="3">
         <v>17600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>10200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>13200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>5000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>9600</v>
       </c>
-      <c r="O42" s="3"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3"/>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>171700</v>
+        <v>95300</v>
       </c>
       <c r="E43" s="3">
-        <v>122200</v>
+        <v>47000</v>
       </c>
       <c r="F43" s="3">
-        <v>144200</v>
+        <v>33400</v>
       </c>
       <c r="G43" s="3">
-        <v>125900</v>
+        <v>39500</v>
       </c>
       <c r="H43" s="3">
-        <v>121300</v>
+        <v>34500</v>
       </c>
       <c r="I43" s="3">
-        <v>60300</v>
+        <v>33200</v>
       </c>
       <c r="J43" s="3">
+        <v>16500</v>
+      </c>
+      <c r="K43" s="3">
         <v>20600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>28200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>27900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>28700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>35300</v>
       </c>
-      <c r="O43" s="3"/>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3"/>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>68500</v>
+        <v>36300</v>
       </c>
       <c r="E44" s="3">
-        <v>42100</v>
+        <v>18700</v>
       </c>
       <c r="F44" s="3">
-        <v>39500</v>
+        <v>11500</v>
       </c>
       <c r="G44" s="3">
-        <v>24700</v>
+        <v>10800</v>
       </c>
       <c r="H44" s="3">
-        <v>18400</v>
+        <v>6800</v>
       </c>
       <c r="I44" s="3">
-        <v>14500</v>
+        <v>5000</v>
       </c>
       <c r="J44" s="3">
+        <v>4000</v>
+      </c>
+      <c r="K44" s="3">
         <v>1900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2600</v>
       </c>
-      <c r="O44" s="3"/>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3"/>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>4700</v>
+        <v>3200</v>
       </c>
       <c r="E45" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="F45" s="3">
-        <v>1500</v>
+        <v>400</v>
       </c>
       <c r="G45" s="3">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="H45" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="I45" s="3">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="J45" s="3">
+        <v>200</v>
+      </c>
+      <c r="K45" s="3">
         <v>400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>7700</v>
       </c>
-      <c r="O45" s="3"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3"/>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>498400</v>
+        <v>281100</v>
       </c>
       <c r="E46" s="3">
-        <v>343900</v>
+        <v>136500</v>
       </c>
       <c r="F46" s="3">
-        <v>351500</v>
+        <v>94200</v>
       </c>
       <c r="G46" s="3">
-        <v>274000</v>
+        <v>96200</v>
       </c>
       <c r="H46" s="3">
-        <v>238500</v>
+        <v>75000</v>
       </c>
       <c r="I46" s="3">
-        <v>99800</v>
+        <v>65300</v>
       </c>
       <c r="J46" s="3">
+        <v>27300</v>
+      </c>
+      <c r="K46" s="3">
         <v>41800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>43700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>43900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>35200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>49700</v>
       </c>
-      <c r="O46" s="3"/>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3"/>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>416800</v>
+        <v>219600</v>
       </c>
       <c r="E47" s="3">
-        <v>255300</v>
+        <v>114100</v>
       </c>
       <c r="F47" s="3">
-        <v>159800</v>
+        <v>69900</v>
       </c>
       <c r="G47" s="3">
-        <v>120700</v>
+        <v>43700</v>
       </c>
       <c r="H47" s="3">
-        <v>88000</v>
+        <v>33100</v>
       </c>
       <c r="I47" s="3">
-        <v>42100</v>
+        <v>24100</v>
       </c>
       <c r="J47" s="3">
+        <v>11500</v>
+      </c>
+      <c r="K47" s="3">
         <v>17900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>22600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>13900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>25600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>41700</v>
       </c>
-      <c r="O47" s="3"/>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3"/>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>739700</v>
+        <v>454300</v>
       </c>
       <c r="E48" s="3">
-        <v>587500</v>
+        <v>202500</v>
       </c>
       <c r="F48" s="3">
-        <v>909300</v>
+        <v>160800</v>
       </c>
       <c r="G48" s="3">
-        <v>597200</v>
+        <v>249000</v>
       </c>
       <c r="H48" s="3">
-        <v>480900</v>
+        <v>163500</v>
       </c>
       <c r="I48" s="3">
-        <v>177200</v>
+        <v>131700</v>
       </c>
       <c r="J48" s="3">
+        <v>48500</v>
+      </c>
+      <c r="K48" s="3">
         <v>62500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>91500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>85200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>199100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>329000</v>
       </c>
-      <c r="O48" s="3"/>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3"/>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>17100</v>
+        <v>28700</v>
       </c>
       <c r="E49" s="3">
-        <v>14900</v>
+        <v>4700</v>
       </c>
       <c r="F49" s="3">
-        <v>39100</v>
+        <v>4100</v>
       </c>
       <c r="G49" s="3">
-        <v>29000</v>
+        <v>10700</v>
       </c>
       <c r="H49" s="3">
-        <v>27400</v>
+        <v>8000</v>
       </c>
       <c r="I49" s="3">
+        <v>7500</v>
+      </c>
+      <c r="J49" s="3">
+        <v>2400</v>
+      </c>
+      <c r="K49" s="3">
+        <v>3200</v>
+      </c>
+      <c r="L49" s="3">
         <v>8700</v>
       </c>
-      <c r="J49" s="3">
-        <v>3200</v>
-      </c>
-      <c r="K49" s="3">
-        <v>8700</v>
-      </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>11100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>59600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>91000</v>
       </c>
-      <c r="O49" s="3"/>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3"/>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2204,9 +2317,12 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-      <c r="O50" s="3"/>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3"/>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2243,48 +2359,54 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-      <c r="O51" s="3"/>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3"/>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>37700</v>
+        <v>7600</v>
       </c>
       <c r="E52" s="3">
-        <v>572100</v>
+        <v>10300</v>
       </c>
       <c r="F52" s="3">
-        <v>7500</v>
+        <v>156600</v>
       </c>
       <c r="G52" s="3">
-        <v>500</v>
+        <v>2100</v>
       </c>
       <c r="H52" s="3">
-        <v>87900</v>
+        <v>100</v>
       </c>
       <c r="I52" s="3">
-        <v>5400</v>
+        <v>24100</v>
       </c>
       <c r="J52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K52" s="3">
         <v>200</v>
-      </c>
-      <c r="K52" s="3">
-        <v>900</v>
       </c>
       <c r="L52" s="3">
         <v>900</v>
       </c>
       <c r="M52" s="3">
+        <v>900</v>
+      </c>
+      <c r="N52" s="3">
         <v>12300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>81600</v>
       </c>
-      <c r="O52" s="3"/>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3"/>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2321,48 +2443,54 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-      <c r="O53" s="3"/>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3"/>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1709600</v>
+        <v>991300</v>
       </c>
       <c r="E54" s="3">
-        <v>1773700</v>
+        <v>468100</v>
       </c>
       <c r="F54" s="3">
-        <v>1467200</v>
+        <v>485600</v>
       </c>
       <c r="G54" s="3">
-        <v>1021500</v>
+        <v>401700</v>
       </c>
       <c r="H54" s="3">
-        <v>919100</v>
+        <v>279700</v>
       </c>
       <c r="I54" s="3">
-        <v>333100</v>
+        <v>251600</v>
       </c>
       <c r="J54" s="3">
+        <v>91200</v>
+      </c>
+      <c r="K54" s="3">
         <v>125600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>167300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>155000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>187100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>316500</v>
       </c>
-      <c r="O54" s="3"/>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3"/>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2378,8 +2506,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2395,242 +2524,261 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>74700</v>
+        <v>44400</v>
       </c>
       <c r="E57" s="3">
-        <v>35400</v>
+        <v>20500</v>
       </c>
       <c r="F57" s="3">
-        <v>97400</v>
+        <v>9700</v>
       </c>
       <c r="G57" s="3">
-        <v>103300</v>
+        <v>26700</v>
       </c>
       <c r="H57" s="3">
-        <v>104600</v>
+        <v>28300</v>
       </c>
       <c r="I57" s="3">
-        <v>54200</v>
+        <v>28600</v>
       </c>
       <c r="J57" s="3">
+        <v>14800</v>
+      </c>
+      <c r="K57" s="3">
         <v>28500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>45000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>38100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>52600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>25300</v>
       </c>
-      <c r="O57" s="3"/>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3"/>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>36900</v>
+        <v>57400</v>
       </c>
       <c r="E58" s="3">
-        <v>87800</v>
+        <v>10100</v>
       </c>
       <c r="F58" s="3">
-        <v>47300</v>
+        <v>24000</v>
       </c>
       <c r="G58" s="3">
-        <v>61600</v>
+        <v>12900</v>
       </c>
       <c r="H58" s="3">
-        <v>37200</v>
+        <v>16900</v>
       </c>
       <c r="I58" s="3">
-        <v>46100</v>
+        <v>10200</v>
       </c>
       <c r="J58" s="3">
+        <v>12600</v>
+      </c>
+      <c r="K58" s="3">
         <v>5600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>7800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>9300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>13100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>47000</v>
       </c>
-      <c r="O58" s="3"/>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3"/>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>39800</v>
+        <v>30000</v>
       </c>
       <c r="E59" s="3">
-        <v>39400</v>
+        <v>10900</v>
       </c>
       <c r="F59" s="3">
-        <v>75600</v>
+        <v>10800</v>
       </c>
       <c r="G59" s="3">
-        <v>48200</v>
+        <v>20700</v>
       </c>
       <c r="H59" s="3">
-        <v>48900</v>
+        <v>13200</v>
       </c>
       <c r="I59" s="3">
-        <v>29300</v>
+        <v>13400</v>
       </c>
       <c r="J59" s="3">
+        <v>8000</v>
+      </c>
+      <c r="K59" s="3">
         <v>7100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>10500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>15200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>24200</v>
       </c>
-      <c r="O59" s="3"/>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3"/>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>151300</v>
+        <v>131800</v>
       </c>
       <c r="E60" s="3">
-        <v>162600</v>
+        <v>41400</v>
       </c>
       <c r="F60" s="3">
-        <v>220300</v>
+        <v>44500</v>
       </c>
       <c r="G60" s="3">
-        <v>213100</v>
+        <v>60300</v>
       </c>
       <c r="H60" s="3">
-        <v>190700</v>
+        <v>58300</v>
       </c>
       <c r="I60" s="3">
-        <v>129600</v>
+        <v>52200</v>
       </c>
       <c r="J60" s="3">
+        <v>35500</v>
+      </c>
+      <c r="K60" s="3">
         <v>41300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>63300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>56900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>53000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>66100</v>
       </c>
-      <c r="O60" s="3"/>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3"/>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>605900</v>
+        <v>282300</v>
       </c>
       <c r="E61" s="3">
-        <v>497500</v>
+        <v>165900</v>
       </c>
       <c r="F61" s="3">
-        <v>455300</v>
+        <v>136200</v>
       </c>
       <c r="G61" s="3">
-        <v>330500</v>
+        <v>124600</v>
       </c>
       <c r="H61" s="3">
-        <v>236300</v>
+        <v>90500</v>
       </c>
       <c r="I61" s="3">
-        <v>65900</v>
+        <v>64700</v>
       </c>
       <c r="J61" s="3">
+        <v>18000</v>
+      </c>
+      <c r="K61" s="3">
         <v>28800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>37600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>36100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>36700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>65100</v>
       </c>
-      <c r="O61" s="3"/>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3"/>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>159100</v>
+        <v>99700</v>
       </c>
       <c r="E62" s="3">
-        <v>101700</v>
+        <v>43600</v>
       </c>
       <c r="F62" s="3">
-        <v>169900</v>
+        <v>27800</v>
       </c>
       <c r="G62" s="3">
-        <v>154600</v>
+        <v>46500</v>
       </c>
       <c r="H62" s="3">
-        <v>157000</v>
+        <v>42300</v>
       </c>
       <c r="I62" s="3">
-        <v>77000</v>
+        <v>43000</v>
       </c>
       <c r="J62" s="3">
+        <v>21100</v>
+      </c>
+      <c r="K62" s="3">
         <v>19400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>31200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>26500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>90700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>73600</v>
       </c>
-      <c r="O62" s="3"/>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3"/>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2667,9 +2815,12 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-      <c r="O63" s="3"/>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3"/>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2706,9 +2857,12 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-      <c r="O64" s="3"/>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3"/>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2745,48 +2899,54 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-      <c r="O65" s="3"/>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3"/>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>919000</v>
+        <v>515200</v>
       </c>
       <c r="E66" s="3">
-        <v>1255400</v>
+        <v>251600</v>
       </c>
       <c r="F66" s="3">
-        <v>972200</v>
+        <v>343700</v>
       </c>
       <c r="G66" s="3">
-        <v>775400</v>
+        <v>266200</v>
       </c>
       <c r="H66" s="3">
-        <v>675700</v>
+        <v>212300</v>
       </c>
       <c r="I66" s="3">
-        <v>285400</v>
+        <v>185000</v>
       </c>
       <c r="J66" s="3">
+        <v>78100</v>
+      </c>
+      <c r="K66" s="3">
         <v>95500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>138300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>129100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>157300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>252600</v>
       </c>
-      <c r="O66" s="3"/>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3"/>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2802,8 +2962,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2840,9 +3001,12 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-      <c r="O68" s="3"/>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3"/>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2879,9 +3043,12 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-      <c r="O69" s="3"/>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3"/>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2918,9 +3085,12 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-      <c r="O70" s="3"/>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3"/>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2957,48 +3127,54 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-      <c r="O71" s="3"/>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3"/>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>446700</v>
+        <v>310900</v>
       </c>
       <c r="E72" s="3">
-        <v>267300</v>
+        <v>122300</v>
       </c>
       <c r="F72" s="3">
-        <v>304100</v>
+        <v>73200</v>
       </c>
       <c r="G72" s="3">
-        <v>109700</v>
+        <v>83300</v>
       </c>
       <c r="H72" s="3">
-        <v>109700</v>
+        <v>30000</v>
       </c>
       <c r="I72" s="3">
+        <v>30000</v>
+      </c>
+      <c r="J72" s="3">
+        <v>4800</v>
+      </c>
+      <c r="K72" s="3">
         <v>17600</v>
       </c>
-      <c r="J72" s="3">
-        <v>17600</v>
-      </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>12800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>6700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-8600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-10400</v>
       </c>
-      <c r="O72" s="3"/>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3"/>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3035,9 +3211,12 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-      <c r="O73" s="3"/>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3"/>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3074,9 +3253,12 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-      <c r="O74" s="3"/>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3"/>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3113,48 +3295,54 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-      <c r="O75" s="3"/>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3"/>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>790600</v>
+        <v>476100</v>
       </c>
       <c r="E76" s="3">
-        <v>518300</v>
+        <v>216400</v>
       </c>
       <c r="F76" s="3">
-        <v>495100</v>
+        <v>141900</v>
       </c>
       <c r="G76" s="3">
-        <v>246100</v>
+        <v>135500</v>
       </c>
       <c r="H76" s="3">
-        <v>243400</v>
+        <v>67400</v>
       </c>
       <c r="I76" s="3">
-        <v>47600</v>
+        <v>66600</v>
       </c>
       <c r="J76" s="3">
+        <v>13000</v>
+      </c>
+      <c r="K76" s="3">
         <v>30100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>29000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>25900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>29800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>63900</v>
       </c>
-      <c r="O76" s="3"/>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3"/>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3191,92 +3379,101 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-      <c r="O77" s="3"/>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3"/>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>44926</v>
+      </c>
+      <c r="E80" s="2">
         <v>44561</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44196</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>43830</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43465</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43100</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>42735</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42369</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42004</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>41639</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41274</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>40908</v>
       </c>
-      <c r="O80" s="2"/>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2"/>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>116800</v>
+        <v>76500</v>
       </c>
       <c r="E81" s="3">
-        <v>-135500</v>
+        <v>32000</v>
       </c>
       <c r="F81" s="3">
-        <v>142300</v>
+        <v>-37100</v>
       </c>
       <c r="G81" s="3">
-        <v>36400</v>
+        <v>39000</v>
       </c>
       <c r="H81" s="3">
-        <v>46500</v>
+        <v>10000</v>
       </c>
       <c r="I81" s="3">
-        <v>0</v>
+        <v>12700</v>
       </c>
       <c r="J81" s="3">
+        <v>0</v>
+      </c>
+      <c r="K81" s="3">
         <v>13200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>7400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-10700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>900</v>
       </c>
-      <c r="O81" s="3"/>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3"/>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3292,47 +3489,51 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>84800</v>
+        <v>32700</v>
       </c>
       <c r="E83" s="3">
-        <v>62400</v>
+        <v>23200</v>
       </c>
       <c r="F83" s="3">
-        <v>60000</v>
+        <v>17100</v>
       </c>
       <c r="G83" s="3">
-        <v>38000</v>
+        <v>16400</v>
       </c>
       <c r="H83" s="3">
-        <v>33400</v>
+        <v>10400</v>
       </c>
       <c r="I83" s="3">
-        <v>9500</v>
+        <v>9100</v>
       </c>
       <c r="J83" s="3">
+        <v>2600</v>
+      </c>
+      <c r="K83" s="3">
         <v>3100</v>
-      </c>
-      <c r="K83" s="3">
-        <v>4600</v>
       </c>
       <c r="L83" s="3">
         <v>4600</v>
       </c>
       <c r="M83" s="3">
+        <v>4600</v>
+      </c>
+      <c r="N83" s="3">
         <v>6200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>10200</v>
       </c>
-      <c r="O83" s="3"/>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3"/>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3369,9 +3570,12 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-      <c r="O84" s="3"/>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3"/>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3408,9 +3612,12 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-      <c r="O85" s="3"/>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3"/>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3447,9 +3654,12 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-      <c r="O86" s="3"/>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3"/>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3486,9 +3696,12 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-      <c r="O87" s="3"/>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3"/>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3525,48 +3738,54 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-      <c r="O88" s="3"/>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3"/>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>329200</v>
+        <v>95800</v>
       </c>
       <c r="E89" s="3">
-        <v>203700</v>
+        <v>90100</v>
       </c>
       <c r="F89" s="3">
-        <v>162500</v>
+        <v>55800</v>
       </c>
       <c r="G89" s="3">
-        <v>98600</v>
+        <v>44500</v>
       </c>
       <c r="H89" s="3">
-        <v>69000</v>
+        <v>27000</v>
       </c>
       <c r="I89" s="3">
-        <v>25600</v>
+        <v>18900</v>
       </c>
       <c r="J89" s="3">
+        <v>7000</v>
+      </c>
+      <c r="K89" s="3">
         <v>18800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>25500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>22200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>19800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>29800</v>
       </c>
-      <c r="O89" s="3"/>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3"/>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3582,47 +3801,51 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-84100</v>
+        <v>-61300</v>
       </c>
       <c r="E91" s="3">
-        <v>-36200</v>
+        <v>-23000</v>
       </c>
       <c r="F91" s="3">
-        <v>-124200</v>
+        <v>-9900</v>
       </c>
       <c r="G91" s="3">
-        <v>-109500</v>
+        <v>-34000</v>
       </c>
       <c r="H91" s="3">
-        <v>-78800</v>
+        <v>-30000</v>
       </c>
       <c r="I91" s="3">
-        <v>-26900</v>
+        <v>-21600</v>
       </c>
       <c r="J91" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="K91" s="3">
         <v>-20700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-23100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-14800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-11300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-42800</v>
       </c>
-      <c r="O91" s="3"/>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3"/>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3659,9 +3882,12 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-      <c r="O92" s="3"/>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3"/>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3698,48 +3924,54 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-      <c r="O93" s="3"/>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3"/>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-197400</v>
+        <v>-88600</v>
       </c>
       <c r="E94" s="3">
-        <v>-66900</v>
+        <v>-54000</v>
       </c>
       <c r="F94" s="3">
-        <v>-74100</v>
+        <v>-18300</v>
       </c>
       <c r="G94" s="3">
-        <v>3200</v>
+        <v>-20300</v>
       </c>
       <c r="H94" s="3">
-        <v>-137700</v>
+        <v>900</v>
       </c>
       <c r="I94" s="3">
-        <v>-48400</v>
+        <v>-37700</v>
       </c>
       <c r="J94" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="K94" s="3">
         <v>-30700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-24500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-19400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-14900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-44900</v>
       </c>
-      <c r="O94" s="3"/>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3"/>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3755,8 +3987,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3764,38 +3997,41 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>-2500</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
+        <v>-700</v>
+      </c>
+      <c r="G96" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H96" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I96" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L96" s="3">
         <v>-200</v>
       </c>
-      <c r="G96" s="3">
-        <v>-400</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-300</v>
-      </c>
-      <c r="I96" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J96" s="3">
-        <v>-100</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-200</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-500</v>
       </c>
-      <c r="O96" s="3"/>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3"/>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3832,9 +4068,12 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-      <c r="O97" s="3"/>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3"/>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3871,9 +4110,12 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-      <c r="O98" s="3"/>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3"/>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3910,124 +4152,136 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-      <c r="O99" s="3"/>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3"/>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-137100</v>
+        <v>-6000</v>
       </c>
       <c r="E100" s="3">
-        <v>-129300</v>
+        <v>-37500</v>
       </c>
       <c r="F100" s="3">
-        <v>-91300</v>
+        <v>-35400</v>
       </c>
       <c r="G100" s="3">
-        <v>-76300</v>
+        <v>-25000</v>
       </c>
       <c r="H100" s="3">
-        <v>60300</v>
+        <v>-20900</v>
       </c>
       <c r="I100" s="3">
-        <v>25100</v>
+        <v>16500</v>
       </c>
       <c r="J100" s="3">
+        <v>6900</v>
+      </c>
+      <c r="K100" s="3">
         <v>12300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-9000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>10300</v>
       </c>
-      <c r="O100" s="3"/>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3"/>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>2500</v>
+        <v>7500</v>
       </c>
       <c r="E101" s="3">
-        <v>-14400</v>
+        <v>700</v>
       </c>
       <c r="F101" s="3">
-        <v>21800</v>
+        <v>-3900</v>
       </c>
       <c r="G101" s="3">
-        <v>8700</v>
+        <v>6000</v>
       </c>
       <c r="H101" s="3">
-        <v>2200</v>
+        <v>2400</v>
       </c>
       <c r="I101" s="3">
-        <v>1600</v>
+        <v>600</v>
       </c>
       <c r="J101" s="3">
+        <v>400</v>
+      </c>
+      <c r="K101" s="3">
         <v>300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>2700</v>
       </c>
-      <c r="O101" s="3"/>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3"/>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-2700</v>
+        <v>8800</v>
       </c>
       <c r="E102" s="3">
-        <v>-6900</v>
+        <v>-700</v>
       </c>
       <c r="F102" s="3">
-        <v>19000</v>
+        <v>-1900</v>
       </c>
       <c r="G102" s="3">
-        <v>34100</v>
+        <v>5200</v>
       </c>
       <c r="H102" s="3">
-        <v>-6200</v>
+        <v>9300</v>
       </c>
       <c r="I102" s="3">
-        <v>3900</v>
+        <v>-1700</v>
       </c>
       <c r="J102" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K102" s="3">
         <v>800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2100</v>
       </c>
-      <c r="O102" s="3"/>
+      <c r="P102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/PAM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PAM_YR_FIN.xlsx
@@ -723,25 +723,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>285800</v>
+        <v>268800</v>
       </c>
       <c r="E8" s="3">
-        <v>170700</v>
+        <v>160600</v>
       </c>
       <c r="F8" s="3">
-        <v>90600</v>
+        <v>85200</v>
       </c>
       <c r="G8" s="3">
-        <v>76300</v>
+        <v>71800</v>
       </c>
       <c r="H8" s="3">
-        <v>63900</v>
+        <v>60100</v>
       </c>
       <c r="I8" s="3">
-        <v>96800</v>
+        <v>91000</v>
       </c>
       <c r="J8" s="3">
-        <v>29600</v>
+        <v>27900</v>
       </c>
       <c r="K8" s="3">
         <v>30900</v>
@@ -765,25 +765,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>178400</v>
+        <v>167800</v>
       </c>
       <c r="E9" s="3">
-        <v>107900</v>
+        <v>101500</v>
       </c>
       <c r="F9" s="3">
-        <v>55900</v>
+        <v>52600</v>
       </c>
       <c r="G9" s="3">
-        <v>46300</v>
+        <v>43500</v>
       </c>
       <c r="H9" s="3">
-        <v>37000</v>
+        <v>34800</v>
       </c>
       <c r="I9" s="3">
-        <v>70700</v>
+        <v>66500</v>
       </c>
       <c r="J9" s="3">
-        <v>21600</v>
+        <v>20300</v>
       </c>
       <c r="K9" s="3">
         <v>29400</v>
@@ -807,25 +807,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>107400</v>
+        <v>101000</v>
       </c>
       <c r="E10" s="3">
-        <v>62800</v>
+        <v>59100</v>
       </c>
       <c r="F10" s="3">
-        <v>34700</v>
+        <v>32700</v>
       </c>
       <c r="G10" s="3">
-        <v>30100</v>
+        <v>28300</v>
       </c>
       <c r="H10" s="3">
-        <v>26800</v>
+        <v>25200</v>
       </c>
       <c r="I10" s="3">
-        <v>26000</v>
+        <v>24500</v>
       </c>
       <c r="J10" s="3">
-        <v>8100</v>
+        <v>7600</v>
       </c>
       <c r="K10" s="3">
         <v>1400</v>
@@ -879,7 +879,7 @@
         <v>500</v>
       </c>
       <c r="H12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I12" s="3">
         <v>100</v>
@@ -951,25 +951,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>8000</v>
+        <v>7500</v>
       </c>
       <c r="E14" s="3">
-        <v>2700</v>
+        <v>2500</v>
       </c>
       <c r="F14" s="3">
-        <v>13500</v>
+        <v>12700</v>
       </c>
       <c r="G14" s="3">
-        <v>6300</v>
+        <v>6000</v>
       </c>
       <c r="H14" s="3">
-        <v>-15800</v>
+        <v>-14800</v>
       </c>
       <c r="I14" s="3">
-        <v>-12300</v>
+        <v>-11500</v>
       </c>
       <c r="J14" s="3">
-        <v>6600</v>
+        <v>6200</v>
       </c>
       <c r="K14" s="3">
         <v>1100</v>
@@ -993,7 +993,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="E15" s="3">
         <v>600</v>
@@ -1050,25 +1050,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>181400</v>
+        <v>170600</v>
       </c>
       <c r="E17" s="3">
-        <v>104000</v>
+        <v>97900</v>
       </c>
       <c r="F17" s="3">
-        <v>69100</v>
+        <v>65000</v>
       </c>
       <c r="G17" s="3">
-        <v>50100</v>
+        <v>47100</v>
       </c>
       <c r="H17" s="3">
-        <v>18400</v>
+        <v>17300</v>
       </c>
       <c r="I17" s="3">
-        <v>66900</v>
+        <v>62900</v>
       </c>
       <c r="J17" s="3">
-        <v>27300</v>
+        <v>25700</v>
       </c>
       <c r="K17" s="3">
         <v>15200</v>
@@ -1092,25 +1092,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>104400</v>
+        <v>98200</v>
       </c>
       <c r="E18" s="3">
-        <v>66700</v>
+        <v>62700</v>
       </c>
       <c r="F18" s="3">
-        <v>21500</v>
+        <v>20200</v>
       </c>
       <c r="G18" s="3">
-        <v>26300</v>
+        <v>24700</v>
       </c>
       <c r="H18" s="3">
-        <v>45500</v>
+        <v>42800</v>
       </c>
       <c r="I18" s="3">
-        <v>29900</v>
+        <v>28100</v>
       </c>
       <c r="J18" s="3">
-        <v>2300</v>
+        <v>2200</v>
       </c>
       <c r="K18" s="3">
         <v>15700</v>
@@ -1152,22 +1152,22 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>22900</v>
+        <v>21500</v>
       </c>
       <c r="E20" s="3">
-        <v>-6300</v>
+        <v>-5900</v>
       </c>
       <c r="F20" s="3">
-        <v>7000</v>
+        <v>6600</v>
       </c>
       <c r="G20" s="3">
-        <v>10200</v>
+        <v>9600</v>
       </c>
       <c r="H20" s="3">
-        <v>-35900</v>
+        <v>-33700</v>
       </c>
       <c r="I20" s="3">
-        <v>-4800</v>
+        <v>-4500</v>
       </c>
       <c r="J20" s="3">
         <v>-500</v>
@@ -1194,25 +1194,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>160000</v>
+        <v>150500</v>
       </c>
       <c r="E21" s="3">
-        <v>83600</v>
+        <v>78700</v>
       </c>
       <c r="F21" s="3">
-        <v>45600</v>
+        <v>42900</v>
       </c>
       <c r="G21" s="3">
-        <v>52900</v>
+        <v>49800</v>
       </c>
       <c r="H21" s="3">
-        <v>20100</v>
+        <v>18900</v>
       </c>
       <c r="I21" s="3">
-        <v>34200</v>
+        <v>32200</v>
       </c>
       <c r="J21" s="3">
-        <v>4400</v>
+        <v>4200</v>
       </c>
       <c r="K21" s="3">
         <v>26300</v>
@@ -1236,25 +1236,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>27800</v>
+        <v>26200</v>
       </c>
       <c r="E22" s="3">
-        <v>15200</v>
+        <v>14300</v>
       </c>
       <c r="F22" s="3">
-        <v>13700</v>
+        <v>12900</v>
       </c>
       <c r="G22" s="3">
-        <v>9400</v>
+        <v>8800</v>
       </c>
       <c r="H22" s="3">
-        <v>7000</v>
+        <v>6600</v>
       </c>
       <c r="I22" s="3">
-        <v>7200</v>
+        <v>6800</v>
       </c>
       <c r="J22" s="3">
-        <v>3600</v>
+        <v>3400</v>
       </c>
       <c r="K22" s="3">
         <v>4000</v>
@@ -1278,25 +1278,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>99500</v>
+        <v>93600</v>
       </c>
       <c r="E23" s="3">
-        <v>45200</v>
+        <v>42500</v>
       </c>
       <c r="F23" s="3">
-        <v>14700</v>
+        <v>13900</v>
       </c>
       <c r="G23" s="3">
-        <v>27100</v>
+        <v>25500</v>
       </c>
       <c r="H23" s="3">
-        <v>2600</v>
+        <v>2500</v>
       </c>
       <c r="I23" s="3">
-        <v>17900</v>
+        <v>16800</v>
       </c>
       <c r="J23" s="3">
-        <v>-1800</v>
+        <v>-1700</v>
       </c>
       <c r="K23" s="3">
         <v>19100</v>
@@ -1320,25 +1320,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>22900</v>
+        <v>21500</v>
       </c>
       <c r="E24" s="3">
-        <v>8600</v>
+        <v>8100</v>
       </c>
       <c r="F24" s="3">
-        <v>3700</v>
+        <v>3500</v>
       </c>
       <c r="G24" s="3">
-        <v>-5300</v>
+        <v>-5000</v>
       </c>
       <c r="H24" s="3">
-        <v>-1400</v>
+        <v>-1300</v>
       </c>
       <c r="I24" s="3">
-        <v>-1200</v>
+        <v>-1100</v>
       </c>
       <c r="J24" s="3">
-        <v>-1400</v>
+        <v>-1300</v>
       </c>
       <c r="K24" s="3">
         <v>2500</v>
@@ -1404,22 +1404,22 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>76600</v>
+        <v>72000</v>
       </c>
       <c r="E26" s="3">
-        <v>36600</v>
+        <v>34400</v>
       </c>
       <c r="F26" s="3">
-        <v>11100</v>
+        <v>10400</v>
       </c>
       <c r="G26" s="3">
-        <v>32400</v>
+        <v>30500</v>
       </c>
       <c r="H26" s="3">
-        <v>4100</v>
+        <v>3800</v>
       </c>
       <c r="I26" s="3">
-        <v>19000</v>
+        <v>17900</v>
       </c>
       <c r="J26" s="3">
         <v>-400</v>
@@ -1446,22 +1446,22 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>76500</v>
+        <v>72000</v>
       </c>
       <c r="E27" s="3">
-        <v>40500</v>
+        <v>38100</v>
       </c>
       <c r="F27" s="3">
-        <v>21100</v>
+        <v>19900</v>
       </c>
       <c r="G27" s="3">
-        <v>25000</v>
+        <v>23500</v>
       </c>
       <c r="H27" s="3">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="I27" s="3">
-        <v>15000</v>
+        <v>14100</v>
       </c>
       <c r="J27" s="3">
         <v>-100</v>
@@ -1533,19 +1533,19 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
-        <v>-8400</v>
+        <v>-7900</v>
       </c>
       <c r="F29" s="3">
-        <v>-58200</v>
+        <v>-54800</v>
       </c>
       <c r="G29" s="3">
-        <v>13900</v>
+        <v>13100</v>
       </c>
       <c r="H29" s="3">
-        <v>8700</v>
+        <v>8200</v>
       </c>
       <c r="I29" s="3">
-        <v>-2200</v>
+        <v>-2100</v>
       </c>
       <c r="J29" s="3">
         <v>100</v>
@@ -1656,22 +1656,22 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-22900</v>
+        <v>-21500</v>
       </c>
       <c r="E32" s="3">
-        <v>6300</v>
+        <v>5900</v>
       </c>
       <c r="F32" s="3">
-        <v>-7000</v>
+        <v>-6600</v>
       </c>
       <c r="G32" s="3">
-        <v>-10200</v>
+        <v>-9600</v>
       </c>
       <c r="H32" s="3">
-        <v>35900</v>
+        <v>33700</v>
       </c>
       <c r="I32" s="3">
-        <v>4800</v>
+        <v>4500</v>
       </c>
       <c r="J32" s="3">
         <v>500</v>
@@ -1698,22 +1698,22 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>76500</v>
+        <v>72000</v>
       </c>
       <c r="E33" s="3">
-        <v>32000</v>
+        <v>30100</v>
       </c>
       <c r="F33" s="3">
-        <v>-37100</v>
+        <v>-34900</v>
       </c>
       <c r="G33" s="3">
-        <v>39000</v>
+        <v>36600</v>
       </c>
       <c r="H33" s="3">
-        <v>10000</v>
+        <v>9400</v>
       </c>
       <c r="I33" s="3">
-        <v>12700</v>
+        <v>12000</v>
       </c>
       <c r="J33" s="3">
         <v>0</v>
@@ -1782,22 +1782,22 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>76500</v>
+        <v>72000</v>
       </c>
       <c r="E35" s="3">
-        <v>32000</v>
+        <v>30100</v>
       </c>
       <c r="F35" s="3">
-        <v>-37100</v>
+        <v>-34900</v>
       </c>
       <c r="G35" s="3">
-        <v>39000</v>
+        <v>36600</v>
       </c>
       <c r="H35" s="3">
-        <v>10000</v>
+        <v>9400</v>
       </c>
       <c r="I35" s="3">
-        <v>12700</v>
+        <v>12000</v>
       </c>
       <c r="J35" s="3">
         <v>0</v>
@@ -1907,25 +1907,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>22100</v>
+        <v>20800</v>
       </c>
       <c r="E41" s="3">
-        <v>13300</v>
+        <v>12500</v>
       </c>
       <c r="F41" s="3">
-        <v>14000</v>
+        <v>13200</v>
       </c>
       <c r="G41" s="3">
-        <v>15900</v>
+        <v>15000</v>
       </c>
       <c r="H41" s="3">
-        <v>11900</v>
+        <v>11200</v>
       </c>
       <c r="I41" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="J41" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="K41" s="3">
         <v>4500</v>
@@ -1949,25 +1949,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>124200</v>
+        <v>116800</v>
       </c>
       <c r="E42" s="3">
-        <v>56100</v>
+        <v>52800</v>
       </c>
       <c r="F42" s="3">
-        <v>34700</v>
+        <v>32700</v>
       </c>
       <c r="G42" s="3">
-        <v>29600</v>
+        <v>27900</v>
       </c>
       <c r="H42" s="3">
-        <v>21700</v>
+        <v>20400</v>
       </c>
       <c r="I42" s="3">
-        <v>25500</v>
+        <v>24000</v>
       </c>
       <c r="J42" s="3">
-        <v>5000</v>
+        <v>4700</v>
       </c>
       <c r="K42" s="3">
         <v>17600</v>
@@ -1991,25 +1991,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>95300</v>
+        <v>89700</v>
       </c>
       <c r="E43" s="3">
-        <v>47000</v>
+        <v>44200</v>
       </c>
       <c r="F43" s="3">
-        <v>33400</v>
+        <v>31500</v>
       </c>
       <c r="G43" s="3">
-        <v>39500</v>
+        <v>37100</v>
       </c>
       <c r="H43" s="3">
-        <v>34500</v>
+        <v>32400</v>
       </c>
       <c r="I43" s="3">
-        <v>33200</v>
+        <v>31200</v>
       </c>
       <c r="J43" s="3">
-        <v>16500</v>
+        <v>15500</v>
       </c>
       <c r="K43" s="3">
         <v>20600</v>
@@ -2033,25 +2033,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>36300</v>
+        <v>34100</v>
       </c>
       <c r="E44" s="3">
-        <v>18700</v>
+        <v>17600</v>
       </c>
       <c r="F44" s="3">
-        <v>11500</v>
+        <v>10800</v>
       </c>
       <c r="G44" s="3">
-        <v>10800</v>
+        <v>10200</v>
       </c>
       <c r="H44" s="3">
-        <v>6800</v>
+        <v>6400</v>
       </c>
       <c r="I44" s="3">
-        <v>5000</v>
+        <v>4700</v>
       </c>
       <c r="J44" s="3">
-        <v>4000</v>
+        <v>3700</v>
       </c>
       <c r="K44" s="3">
         <v>1900</v>
@@ -2075,10 +2075,10 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>3200</v>
+        <v>3000</v>
       </c>
       <c r="E45" s="3">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="F45" s="3">
         <v>400</v>
@@ -2117,25 +2117,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>281100</v>
+        <v>264400</v>
       </c>
       <c r="E46" s="3">
-        <v>136500</v>
+        <v>128400</v>
       </c>
       <c r="F46" s="3">
-        <v>94200</v>
+        <v>88600</v>
       </c>
       <c r="G46" s="3">
-        <v>96200</v>
+        <v>90500</v>
       </c>
       <c r="H46" s="3">
-        <v>75000</v>
+        <v>70600</v>
       </c>
       <c r="I46" s="3">
-        <v>65300</v>
+        <v>61400</v>
       </c>
       <c r="J46" s="3">
-        <v>27300</v>
+        <v>25700</v>
       </c>
       <c r="K46" s="3">
         <v>41800</v>
@@ -2159,25 +2159,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>219600</v>
+        <v>206600</v>
       </c>
       <c r="E47" s="3">
-        <v>114100</v>
+        <v>107300</v>
       </c>
       <c r="F47" s="3">
-        <v>69900</v>
+        <v>65700</v>
       </c>
       <c r="G47" s="3">
-        <v>43700</v>
+        <v>41100</v>
       </c>
       <c r="H47" s="3">
-        <v>33100</v>
+        <v>31100</v>
       </c>
       <c r="I47" s="3">
-        <v>24100</v>
+        <v>22700</v>
       </c>
       <c r="J47" s="3">
-        <v>11500</v>
+        <v>10800</v>
       </c>
       <c r="K47" s="3">
         <v>17900</v>
@@ -2201,25 +2201,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>454300</v>
+        <v>427300</v>
       </c>
       <c r="E48" s="3">
-        <v>202500</v>
+        <v>190500</v>
       </c>
       <c r="F48" s="3">
-        <v>160800</v>
+        <v>151300</v>
       </c>
       <c r="G48" s="3">
-        <v>249000</v>
+        <v>234200</v>
       </c>
       <c r="H48" s="3">
-        <v>163500</v>
+        <v>153800</v>
       </c>
       <c r="I48" s="3">
-        <v>131700</v>
+        <v>123800</v>
       </c>
       <c r="J48" s="3">
-        <v>48500</v>
+        <v>45600</v>
       </c>
       <c r="K48" s="3">
         <v>62500</v>
@@ -2243,25 +2243,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>28700</v>
+        <v>27000</v>
       </c>
       <c r="E49" s="3">
-        <v>4700</v>
+        <v>4400</v>
       </c>
       <c r="F49" s="3">
-        <v>4100</v>
+        <v>3800</v>
       </c>
       <c r="G49" s="3">
-        <v>10700</v>
+        <v>10100</v>
       </c>
       <c r="H49" s="3">
-        <v>8000</v>
+        <v>7500</v>
       </c>
       <c r="I49" s="3">
-        <v>7500</v>
+        <v>7100</v>
       </c>
       <c r="J49" s="3">
-        <v>2400</v>
+        <v>2200</v>
       </c>
       <c r="K49" s="3">
         <v>3200</v>
@@ -2369,25 +2369,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>7600</v>
+        <v>7100</v>
       </c>
       <c r="E52" s="3">
-        <v>10300</v>
+        <v>9700</v>
       </c>
       <c r="F52" s="3">
-        <v>156600</v>
+        <v>147300</v>
       </c>
       <c r="G52" s="3">
-        <v>2100</v>
+        <v>1900</v>
       </c>
       <c r="H52" s="3">
         <v>100</v>
       </c>
       <c r="I52" s="3">
-        <v>24100</v>
+        <v>22600</v>
       </c>
       <c r="J52" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="K52" s="3">
         <v>200</v>
@@ -2453,25 +2453,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>991300</v>
+        <v>932500</v>
       </c>
       <c r="E54" s="3">
-        <v>468100</v>
+        <v>440300</v>
       </c>
       <c r="F54" s="3">
-        <v>485600</v>
+        <v>456800</v>
       </c>
       <c r="G54" s="3">
-        <v>401700</v>
+        <v>377900</v>
       </c>
       <c r="H54" s="3">
-        <v>279700</v>
+        <v>263100</v>
       </c>
       <c r="I54" s="3">
-        <v>251600</v>
+        <v>236700</v>
       </c>
       <c r="J54" s="3">
-        <v>91200</v>
+        <v>85800</v>
       </c>
       <c r="K54" s="3">
         <v>125600</v>
@@ -2531,25 +2531,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>44400</v>
+        <v>41800</v>
       </c>
       <c r="E57" s="3">
-        <v>20500</v>
+        <v>19200</v>
       </c>
       <c r="F57" s="3">
-        <v>9700</v>
+        <v>9100</v>
       </c>
       <c r="G57" s="3">
-        <v>26700</v>
+        <v>25100</v>
       </c>
       <c r="H57" s="3">
-        <v>28300</v>
+        <v>26600</v>
       </c>
       <c r="I57" s="3">
-        <v>28600</v>
+        <v>26900</v>
       </c>
       <c r="J57" s="3">
-        <v>14800</v>
+        <v>14000</v>
       </c>
       <c r="K57" s="3">
         <v>28500</v>
@@ -2573,25 +2573,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>57400</v>
+        <v>54000</v>
       </c>
       <c r="E58" s="3">
-        <v>10100</v>
+        <v>9500</v>
       </c>
       <c r="F58" s="3">
-        <v>24000</v>
+        <v>22600</v>
       </c>
       <c r="G58" s="3">
-        <v>12900</v>
+        <v>12200</v>
       </c>
       <c r="H58" s="3">
-        <v>16900</v>
+        <v>15900</v>
       </c>
       <c r="I58" s="3">
-        <v>10200</v>
+        <v>9600</v>
       </c>
       <c r="J58" s="3">
-        <v>12600</v>
+        <v>11900</v>
       </c>
       <c r="K58" s="3">
         <v>5600</v>
@@ -2615,25 +2615,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>30000</v>
+        <v>28200</v>
       </c>
       <c r="E59" s="3">
-        <v>10900</v>
+        <v>10200</v>
       </c>
       <c r="F59" s="3">
-        <v>10800</v>
+        <v>10100</v>
       </c>
       <c r="G59" s="3">
-        <v>20700</v>
+        <v>19500</v>
       </c>
       <c r="H59" s="3">
-        <v>13200</v>
+        <v>12400</v>
       </c>
       <c r="I59" s="3">
-        <v>13400</v>
+        <v>12600</v>
       </c>
       <c r="J59" s="3">
-        <v>8000</v>
+        <v>7600</v>
       </c>
       <c r="K59" s="3">
         <v>7100</v>
@@ -2657,25 +2657,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>131800</v>
+        <v>124000</v>
       </c>
       <c r="E60" s="3">
-        <v>41400</v>
+        <v>39000</v>
       </c>
       <c r="F60" s="3">
-        <v>44500</v>
+        <v>41900</v>
       </c>
       <c r="G60" s="3">
-        <v>60300</v>
+        <v>56700</v>
       </c>
       <c r="H60" s="3">
-        <v>58300</v>
+        <v>54900</v>
       </c>
       <c r="I60" s="3">
-        <v>52200</v>
+        <v>49100</v>
       </c>
       <c r="J60" s="3">
-        <v>35500</v>
+        <v>33400</v>
       </c>
       <c r="K60" s="3">
         <v>41300</v>
@@ -2699,25 +2699,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>282300</v>
+        <v>265500</v>
       </c>
       <c r="E61" s="3">
-        <v>165900</v>
+        <v>156000</v>
       </c>
       <c r="F61" s="3">
-        <v>136200</v>
+        <v>128100</v>
       </c>
       <c r="G61" s="3">
-        <v>124600</v>
+        <v>117200</v>
       </c>
       <c r="H61" s="3">
-        <v>90500</v>
+        <v>85100</v>
       </c>
       <c r="I61" s="3">
-        <v>64700</v>
+        <v>60800</v>
       </c>
       <c r="J61" s="3">
-        <v>18000</v>
+        <v>17000</v>
       </c>
       <c r="K61" s="3">
         <v>28800</v>
@@ -2741,25 +2741,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>99700</v>
+        <v>93800</v>
       </c>
       <c r="E62" s="3">
-        <v>43600</v>
+        <v>41000</v>
       </c>
       <c r="F62" s="3">
-        <v>27800</v>
+        <v>26200</v>
       </c>
       <c r="G62" s="3">
-        <v>46500</v>
+        <v>43800</v>
       </c>
       <c r="H62" s="3">
-        <v>42300</v>
+        <v>39800</v>
       </c>
       <c r="I62" s="3">
-        <v>43000</v>
+        <v>40400</v>
       </c>
       <c r="J62" s="3">
-        <v>21100</v>
+        <v>19800</v>
       </c>
       <c r="K62" s="3">
         <v>19400</v>
@@ -2909,25 +2909,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>515200</v>
+        <v>484600</v>
       </c>
       <c r="E66" s="3">
-        <v>251600</v>
+        <v>236700</v>
       </c>
       <c r="F66" s="3">
-        <v>343700</v>
+        <v>323300</v>
       </c>
       <c r="G66" s="3">
-        <v>266200</v>
+        <v>250400</v>
       </c>
       <c r="H66" s="3">
-        <v>212300</v>
+        <v>199700</v>
       </c>
       <c r="I66" s="3">
-        <v>185000</v>
+        <v>174000</v>
       </c>
       <c r="J66" s="3">
-        <v>78100</v>
+        <v>73500</v>
       </c>
       <c r="K66" s="3">
         <v>95500</v>
@@ -3137,25 +3137,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>310900</v>
+        <v>292400</v>
       </c>
       <c r="E72" s="3">
-        <v>122300</v>
+        <v>115000</v>
       </c>
       <c r="F72" s="3">
-        <v>73200</v>
+        <v>68800</v>
       </c>
       <c r="G72" s="3">
-        <v>83300</v>
+        <v>78300</v>
       </c>
       <c r="H72" s="3">
-        <v>30000</v>
+        <v>28300</v>
       </c>
       <c r="I72" s="3">
-        <v>30000</v>
+        <v>28300</v>
       </c>
       <c r="J72" s="3">
-        <v>4800</v>
+        <v>4500</v>
       </c>
       <c r="K72" s="3">
         <v>17600</v>
@@ -3305,25 +3305,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>476100</v>
+        <v>447800</v>
       </c>
       <c r="E76" s="3">
-        <v>216400</v>
+        <v>203600</v>
       </c>
       <c r="F76" s="3">
-        <v>141900</v>
+        <v>133500</v>
       </c>
       <c r="G76" s="3">
-        <v>135500</v>
+        <v>127500</v>
       </c>
       <c r="H76" s="3">
-        <v>67400</v>
+        <v>63400</v>
       </c>
       <c r="I76" s="3">
-        <v>66600</v>
+        <v>62700</v>
       </c>
       <c r="J76" s="3">
-        <v>13000</v>
+        <v>12300</v>
       </c>
       <c r="K76" s="3">
         <v>30100</v>
@@ -3436,22 +3436,22 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>76500</v>
+        <v>72000</v>
       </c>
       <c r="E81" s="3">
-        <v>32000</v>
+        <v>30100</v>
       </c>
       <c r="F81" s="3">
-        <v>-37100</v>
+        <v>-34900</v>
       </c>
       <c r="G81" s="3">
-        <v>39000</v>
+        <v>36600</v>
       </c>
       <c r="H81" s="3">
-        <v>10000</v>
+        <v>9400</v>
       </c>
       <c r="I81" s="3">
-        <v>12700</v>
+        <v>12000</v>
       </c>
       <c r="J81" s="3">
         <v>0</v>
@@ -3496,25 +3496,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>32700</v>
+        <v>30800</v>
       </c>
       <c r="E83" s="3">
-        <v>23200</v>
+        <v>21800</v>
       </c>
       <c r="F83" s="3">
-        <v>17100</v>
+        <v>16100</v>
       </c>
       <c r="G83" s="3">
-        <v>16400</v>
+        <v>15500</v>
       </c>
       <c r="H83" s="3">
-        <v>10400</v>
+        <v>9800</v>
       </c>
       <c r="I83" s="3">
-        <v>9100</v>
+        <v>8600</v>
       </c>
       <c r="J83" s="3">
-        <v>2600</v>
+        <v>2400</v>
       </c>
       <c r="K83" s="3">
         <v>3100</v>
@@ -3748,25 +3748,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>95800</v>
+        <v>90100</v>
       </c>
       <c r="E89" s="3">
-        <v>90100</v>
+        <v>84800</v>
       </c>
       <c r="F89" s="3">
-        <v>55800</v>
+        <v>52500</v>
       </c>
       <c r="G89" s="3">
-        <v>44500</v>
+        <v>41800</v>
       </c>
       <c r="H89" s="3">
-        <v>27000</v>
+        <v>25400</v>
       </c>
       <c r="I89" s="3">
-        <v>18900</v>
+        <v>17800</v>
       </c>
       <c r="J89" s="3">
-        <v>7000</v>
+        <v>6600</v>
       </c>
       <c r="K89" s="3">
         <v>18800</v>
@@ -3808,25 +3808,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-61300</v>
+        <v>-57600</v>
       </c>
       <c r="E91" s="3">
-        <v>-23000</v>
+        <v>-21700</v>
       </c>
       <c r="F91" s="3">
-        <v>-9900</v>
+        <v>-9300</v>
       </c>
       <c r="G91" s="3">
-        <v>-34000</v>
+        <v>-32000</v>
       </c>
       <c r="H91" s="3">
-        <v>-30000</v>
+        <v>-28200</v>
       </c>
       <c r="I91" s="3">
-        <v>-21600</v>
+        <v>-20300</v>
       </c>
       <c r="J91" s="3">
-        <v>-7400</v>
+        <v>-6900</v>
       </c>
       <c r="K91" s="3">
         <v>-20700</v>
@@ -3934,25 +3934,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-88600</v>
+        <v>-83300</v>
       </c>
       <c r="E94" s="3">
-        <v>-54000</v>
+        <v>-50800</v>
       </c>
       <c r="F94" s="3">
-        <v>-18300</v>
+        <v>-17200</v>
       </c>
       <c r="G94" s="3">
-        <v>-20300</v>
+        <v>-19100</v>
       </c>
       <c r="H94" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="I94" s="3">
-        <v>-37700</v>
+        <v>-35500</v>
       </c>
       <c r="J94" s="3">
-        <v>-13300</v>
+        <v>-12500</v>
       </c>
       <c r="K94" s="3">
         <v>-30700</v>
@@ -4162,25 +4162,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-6000</v>
+        <v>-5600</v>
       </c>
       <c r="E100" s="3">
-        <v>-37500</v>
+        <v>-35300</v>
       </c>
       <c r="F100" s="3">
-        <v>-35400</v>
+        <v>-33300</v>
       </c>
       <c r="G100" s="3">
-        <v>-25000</v>
+        <v>-23500</v>
       </c>
       <c r="H100" s="3">
-        <v>-20900</v>
+        <v>-19700</v>
       </c>
       <c r="I100" s="3">
-        <v>16500</v>
+        <v>15500</v>
       </c>
       <c r="J100" s="3">
-        <v>6900</v>
+        <v>6500</v>
       </c>
       <c r="K100" s="3">
         <v>12300</v>
@@ -4204,19 +4204,19 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>7500</v>
+        <v>7100</v>
       </c>
       <c r="E101" s="3">
         <v>700</v>
       </c>
       <c r="F101" s="3">
-        <v>-3900</v>
+        <v>-3700</v>
       </c>
       <c r="G101" s="3">
-        <v>6000</v>
+        <v>5600</v>
       </c>
       <c r="H101" s="3">
-        <v>2400</v>
+        <v>2200</v>
       </c>
       <c r="I101" s="3">
         <v>600</v>
@@ -4246,25 +4246,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>8800</v>
+        <v>8300</v>
       </c>
       <c r="E102" s="3">
         <v>-700</v>
       </c>
       <c r="F102" s="3">
-        <v>-1900</v>
+        <v>-1800</v>
       </c>
       <c r="G102" s="3">
-        <v>5200</v>
+        <v>4900</v>
       </c>
       <c r="H102" s="3">
-        <v>9300</v>
+        <v>8800</v>
       </c>
       <c r="I102" s="3">
-        <v>-1700</v>
+        <v>-1600</v>
       </c>
       <c r="J102" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="K102" s="3">
         <v>800</v>

--- a/AAII_Financials/Yearly/PAM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PAM_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="92">
   <si>
     <t>PAM</t>
   </si>
@@ -656,195 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>268800</v>
+        <v>534300</v>
       </c>
       <c r="E8" s="3">
-        <v>160600</v>
+        <v>251900</v>
       </c>
       <c r="F8" s="3">
-        <v>85200</v>
+        <v>150400</v>
       </c>
       <c r="G8" s="3">
-        <v>71800</v>
+        <v>79800</v>
       </c>
       <c r="H8" s="3">
-        <v>60100</v>
+        <v>67300</v>
       </c>
       <c r="I8" s="3">
-        <v>91000</v>
+        <v>56300</v>
       </c>
       <c r="J8" s="3">
+        <v>85300</v>
+      </c>
+      <c r="K8" s="3">
         <v>27900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>30900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>61600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>65800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>110700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>136900</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>167800</v>
+        <v>333400</v>
       </c>
       <c r="E9" s="3">
-        <v>101500</v>
+        <v>157300</v>
       </c>
       <c r="F9" s="3">
-        <v>52600</v>
+        <v>95100</v>
       </c>
       <c r="G9" s="3">
-        <v>43500</v>
+        <v>49200</v>
       </c>
       <c r="H9" s="3">
-        <v>34800</v>
+        <v>40800</v>
       </c>
       <c r="I9" s="3">
-        <v>66500</v>
+        <v>32600</v>
       </c>
       <c r="J9" s="3">
+        <v>62300</v>
+      </c>
+      <c r="K9" s="3">
         <v>20300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>29400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>59800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>69100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>220500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>257900</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>101000</v>
+        <v>200900</v>
       </c>
       <c r="E10" s="3">
-        <v>59100</v>
+        <v>94600</v>
       </c>
       <c r="F10" s="3">
-        <v>32700</v>
+        <v>55300</v>
       </c>
       <c r="G10" s="3">
-        <v>28300</v>
+        <v>30600</v>
       </c>
       <c r="H10" s="3">
-        <v>25200</v>
+        <v>26500</v>
       </c>
       <c r="I10" s="3">
-        <v>24500</v>
+        <v>23700</v>
       </c>
       <c r="J10" s="3">
+        <v>22900</v>
+      </c>
+      <c r="K10" s="3">
         <v>7600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-3300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-109800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-120900</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,34 +873,35 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E12" s="3">
         <v>100</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3">
         <v>500</v>
       </c>
-      <c r="H12" s="3">
-        <v>0</v>
-      </c>
       <c r="I12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J12" s="3">
         <v>100</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>8</v>
+      <c r="K12" s="3">
+        <v>100</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>8</v>
@@ -902,9 +915,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,93 +960,102 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>7500</v>
+        <v>32400</v>
       </c>
       <c r="E14" s="3">
-        <v>2500</v>
+        <v>7000</v>
       </c>
       <c r="F14" s="3">
-        <v>12700</v>
+        <v>2300</v>
       </c>
       <c r="G14" s="3">
-        <v>6000</v>
+        <v>11900</v>
       </c>
       <c r="H14" s="3">
-        <v>-14800</v>
+        <v>5600</v>
       </c>
       <c r="I14" s="3">
-        <v>-11500</v>
+        <v>-13900</v>
       </c>
       <c r="J14" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="K14" s="3">
         <v>6200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>34200</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E15" s="3">
         <v>800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
+        <v>500</v>
+      </c>
+      <c r="G15" s="3">
+        <v>400</v>
+      </c>
+      <c r="H15" s="3">
+        <v>500</v>
+      </c>
+      <c r="I15" s="3">
+        <v>200</v>
+      </c>
+      <c r="J15" s="3">
+        <v>400</v>
+      </c>
+      <c r="K15" s="3">
+        <v>100</v>
+      </c>
+      <c r="L15" s="3">
+        <v>200</v>
+      </c>
+      <c r="M15" s="3">
+        <v>400</v>
+      </c>
+      <c r="N15" s="3">
+        <v>300</v>
+      </c>
+      <c r="O15" s="3">
+        <v>500</v>
+      </c>
+      <c r="P15" s="3">
         <v>600</v>
       </c>
-      <c r="F15" s="3">
-        <v>400</v>
-      </c>
-      <c r="G15" s="3">
-        <v>500</v>
-      </c>
-      <c r="H15" s="3">
-        <v>300</v>
-      </c>
-      <c r="I15" s="3">
-        <v>400</v>
-      </c>
-      <c r="J15" s="3">
-        <v>100</v>
-      </c>
-      <c r="K15" s="3">
-        <v>200</v>
-      </c>
-      <c r="L15" s="3">
-        <v>400</v>
-      </c>
-      <c r="M15" s="3">
-        <v>300</v>
-      </c>
-      <c r="N15" s="3">
-        <v>500</v>
-      </c>
-      <c r="O15" s="3">
-        <v>600</v>
-      </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>170600</v>
+        <v>411800</v>
       </c>
       <c r="E17" s="3">
-        <v>97900</v>
+        <v>159900</v>
       </c>
       <c r="F17" s="3">
-        <v>65000</v>
+        <v>91700</v>
       </c>
       <c r="G17" s="3">
-        <v>47100</v>
+        <v>60900</v>
       </c>
       <c r="H17" s="3">
-        <v>17300</v>
+        <v>44100</v>
       </c>
       <c r="I17" s="3">
-        <v>62900</v>
+        <v>16200</v>
       </c>
       <c r="J17" s="3">
+        <v>58900</v>
+      </c>
+      <c r="K17" s="3">
         <v>25700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>15200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>52800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>44500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>122000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>144700</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>98200</v>
+        <v>122500</v>
       </c>
       <c r="E18" s="3">
-        <v>62700</v>
+        <v>92000</v>
       </c>
       <c r="F18" s="3">
-        <v>20200</v>
+        <v>58700</v>
       </c>
       <c r="G18" s="3">
-        <v>24700</v>
+        <v>18900</v>
       </c>
       <c r="H18" s="3">
-        <v>42800</v>
+        <v>23200</v>
       </c>
       <c r="I18" s="3">
-        <v>28100</v>
+        <v>40100</v>
       </c>
       <c r="J18" s="3">
+        <v>26400</v>
+      </c>
+      <c r="K18" s="3">
         <v>2200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>15700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>8800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>21300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-11300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-7800</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1146,218 +1178,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>21500</v>
+        <v>145400</v>
       </c>
       <c r="E20" s="3">
-        <v>-5900</v>
+        <v>20200</v>
       </c>
       <c r="F20" s="3">
-        <v>6600</v>
+        <v>-5500</v>
       </c>
       <c r="G20" s="3">
-        <v>9600</v>
+        <v>6200</v>
       </c>
       <c r="H20" s="3">
-        <v>-33700</v>
+        <v>9000</v>
       </c>
       <c r="I20" s="3">
-        <v>-4500</v>
+        <v>-31600</v>
       </c>
       <c r="J20" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="K20" s="3">
         <v>-500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>7500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>7100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-3000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>7000</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>150500</v>
+        <v>350500</v>
       </c>
       <c r="E21" s="3">
-        <v>78700</v>
+        <v>141000</v>
       </c>
       <c r="F21" s="3">
-        <v>42900</v>
+        <v>73600</v>
       </c>
       <c r="G21" s="3">
-        <v>49800</v>
+        <v>40200</v>
       </c>
       <c r="H21" s="3">
-        <v>18900</v>
+        <v>46600</v>
       </c>
       <c r="I21" s="3">
-        <v>32200</v>
+        <v>17700</v>
       </c>
       <c r="J21" s="3">
+        <v>30200</v>
+      </c>
+      <c r="K21" s="3">
         <v>4200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>26300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>20500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>22900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-7900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>9600</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>26200</v>
+        <v>91800</v>
       </c>
       <c r="E22" s="3">
-        <v>14300</v>
+        <v>24500</v>
       </c>
       <c r="F22" s="3">
-        <v>12900</v>
+        <v>13400</v>
       </c>
       <c r="G22" s="3">
-        <v>8800</v>
+        <v>12100</v>
       </c>
       <c r="H22" s="3">
-        <v>6600</v>
+        <v>8300</v>
       </c>
       <c r="I22" s="3">
-        <v>6800</v>
+        <v>6200</v>
       </c>
       <c r="J22" s="3">
+        <v>6400</v>
+      </c>
+      <c r="K22" s="3">
         <v>3400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>4000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>9600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>9300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>6500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>19200</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>93600</v>
+        <v>176000</v>
       </c>
       <c r="E23" s="3">
-        <v>42500</v>
+        <v>87700</v>
       </c>
       <c r="F23" s="3">
-        <v>13900</v>
+        <v>39700</v>
       </c>
       <c r="G23" s="3">
-        <v>25500</v>
+        <v>13000</v>
       </c>
       <c r="H23" s="3">
-        <v>2500</v>
+        <v>23900</v>
       </c>
       <c r="I23" s="3">
-        <v>16800</v>
+        <v>2300</v>
       </c>
       <c r="J23" s="3">
+        <v>15800</v>
+      </c>
+      <c r="K23" s="3">
         <v>-1700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>19100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>6200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>9000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-20600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-20100</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>21500</v>
+        <v>137900</v>
       </c>
       <c r="E24" s="3">
-        <v>8100</v>
+        <v>20200</v>
       </c>
       <c r="F24" s="3">
-        <v>3500</v>
+        <v>7600</v>
       </c>
       <c r="G24" s="3">
-        <v>-5000</v>
+        <v>3200</v>
       </c>
       <c r="H24" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="I24" s="3">
         <v>-1300</v>
       </c>
-      <c r="I24" s="3">
-        <v>-1100</v>
-      </c>
       <c r="J24" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="K24" s="3">
         <v>-1300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-2200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-1000</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>72000</v>
+        <v>38200</v>
       </c>
       <c r="E26" s="3">
-        <v>34400</v>
+        <v>67500</v>
       </c>
       <c r="F26" s="3">
-        <v>10400</v>
+        <v>32200</v>
       </c>
       <c r="G26" s="3">
-        <v>30500</v>
+        <v>9700</v>
       </c>
       <c r="H26" s="3">
-        <v>3800</v>
+        <v>28600</v>
       </c>
       <c r="I26" s="3">
-        <v>17900</v>
+        <v>3600</v>
       </c>
       <c r="J26" s="3">
+        <v>16800</v>
+      </c>
+      <c r="K26" s="3">
         <v>-400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>16600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>9200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-18400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-19100</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>72000</v>
+        <v>35900</v>
       </c>
       <c r="E27" s="3">
-        <v>38100</v>
+        <v>67500</v>
       </c>
       <c r="F27" s="3">
-        <v>19900</v>
+        <v>35600</v>
       </c>
       <c r="G27" s="3">
-        <v>23500</v>
+        <v>18600</v>
       </c>
       <c r="H27" s="3">
-        <v>1200</v>
+        <v>22000</v>
       </c>
       <c r="I27" s="3">
-        <v>14100</v>
+        <v>1100</v>
       </c>
       <c r="J27" s="3">
+        <v>13200</v>
+      </c>
+      <c r="K27" s="3">
         <v>-100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>13200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>7400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-11300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3300</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1523,9 +1580,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1533,41 +1593,44 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
-        <v>-7900</v>
+        <v>0</v>
       </c>
       <c r="F29" s="3">
-        <v>-54800</v>
+        <v>-7400</v>
       </c>
       <c r="G29" s="3">
-        <v>13100</v>
+        <v>-51300</v>
       </c>
       <c r="H29" s="3">
-        <v>8200</v>
+        <v>12300</v>
       </c>
       <c r="I29" s="3">
-        <v>-2100</v>
+        <v>7700</v>
       </c>
       <c r="J29" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="K29" s="3">
         <v>100</v>
       </c>
-      <c r="K29" s="3" t="s">
+      <c r="L29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>-1600</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>500</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-2400</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,93 +1715,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-21500</v>
+        <v>-145400</v>
       </c>
       <c r="E32" s="3">
-        <v>5900</v>
+        <v>-20200</v>
       </c>
       <c r="F32" s="3">
-        <v>-6600</v>
+        <v>5500</v>
       </c>
       <c r="G32" s="3">
-        <v>-9600</v>
+        <v>-6200</v>
       </c>
       <c r="H32" s="3">
-        <v>33700</v>
+        <v>-9000</v>
       </c>
       <c r="I32" s="3">
-        <v>4500</v>
+        <v>31600</v>
       </c>
       <c r="J32" s="3">
+        <v>4200</v>
+      </c>
+      <c r="K32" s="3">
         <v>500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-7500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-7100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>3000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-7000</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>72000</v>
+        <v>35900</v>
       </c>
       <c r="E33" s="3">
-        <v>30100</v>
+        <v>67500</v>
       </c>
       <c r="F33" s="3">
-        <v>-34900</v>
+        <v>28200</v>
       </c>
       <c r="G33" s="3">
-        <v>36600</v>
+        <v>-32700</v>
       </c>
       <c r="H33" s="3">
-        <v>9400</v>
+        <v>34300</v>
       </c>
       <c r="I33" s="3">
-        <v>12000</v>
+        <v>8800</v>
       </c>
       <c r="J33" s="3">
-        <v>0</v>
+        <v>11200</v>
       </c>
       <c r="K33" s="3">
+        <v>0</v>
+      </c>
+      <c r="L33" s="3">
         <v>13200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>7400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-10700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>900</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>72000</v>
+        <v>35900</v>
       </c>
       <c r="E35" s="3">
-        <v>30100</v>
+        <v>67500</v>
       </c>
       <c r="F35" s="3">
-        <v>-34900</v>
+        <v>28200</v>
       </c>
       <c r="G35" s="3">
-        <v>36600</v>
+        <v>-32700</v>
       </c>
       <c r="H35" s="3">
-        <v>9400</v>
+        <v>34300</v>
       </c>
       <c r="I35" s="3">
-        <v>12000</v>
+        <v>8800</v>
       </c>
       <c r="J35" s="3">
-        <v>0</v>
+        <v>11200</v>
       </c>
       <c r="K35" s="3">
+        <v>0</v>
+      </c>
+      <c r="L35" s="3">
         <v>13200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>7400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-10700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>900</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,386 +1986,414 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>20800</v>
+        <v>143500</v>
       </c>
       <c r="E41" s="3">
-        <v>12500</v>
+        <v>19500</v>
       </c>
       <c r="F41" s="3">
-        <v>13200</v>
+        <v>11700</v>
       </c>
       <c r="G41" s="3">
-        <v>15000</v>
+        <v>12400</v>
       </c>
       <c r="H41" s="3">
-        <v>11200</v>
+        <v>14000</v>
       </c>
       <c r="I41" s="3">
-        <v>1300</v>
+        <v>10500</v>
       </c>
       <c r="J41" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K41" s="3">
         <v>1600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9000</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>116800</v>
+        <v>558100</v>
       </c>
       <c r="E42" s="3">
-        <v>52800</v>
+        <v>109400</v>
       </c>
       <c r="F42" s="3">
-        <v>32700</v>
+        <v>49500</v>
       </c>
       <c r="G42" s="3">
-        <v>27900</v>
+        <v>30600</v>
       </c>
       <c r="H42" s="3">
-        <v>20400</v>
+        <v>26100</v>
       </c>
       <c r="I42" s="3">
-        <v>24000</v>
+        <v>19100</v>
       </c>
       <c r="J42" s="3">
+        <v>22500</v>
+      </c>
+      <c r="K42" s="3">
         <v>4700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>17600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>10200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>13200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>5000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>9600</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>89700</v>
+        <v>243400</v>
       </c>
       <c r="E43" s="3">
-        <v>44200</v>
+        <v>84000</v>
       </c>
       <c r="F43" s="3">
-        <v>31500</v>
+        <v>41400</v>
       </c>
       <c r="G43" s="3">
-        <v>37100</v>
+        <v>29500</v>
       </c>
       <c r="H43" s="3">
-        <v>32400</v>
+        <v>34800</v>
       </c>
       <c r="I43" s="3">
-        <v>31200</v>
+        <v>30400</v>
       </c>
       <c r="J43" s="3">
+        <v>29300</v>
+      </c>
+      <c r="K43" s="3">
         <v>15500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>20600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>28200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>27900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>28700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>35300</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>34100</v>
+        <v>172700</v>
       </c>
       <c r="E44" s="3">
-        <v>17600</v>
+        <v>32000</v>
       </c>
       <c r="F44" s="3">
-        <v>10800</v>
+        <v>16500</v>
       </c>
       <c r="G44" s="3">
         <v>10200</v>
       </c>
       <c r="H44" s="3">
-        <v>6400</v>
+        <v>9500</v>
       </c>
       <c r="I44" s="3">
-        <v>4700</v>
+        <v>6000</v>
       </c>
       <c r="J44" s="3">
+        <v>4400</v>
+      </c>
+      <c r="K44" s="3">
         <v>3700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2600</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>3000</v>
+        <v>4700</v>
       </c>
       <c r="E45" s="3">
-        <v>1200</v>
+        <v>2800</v>
       </c>
       <c r="F45" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G45" s="3">
+        <v>300</v>
+      </c>
+      <c r="H45" s="3">
         <v>400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
+        <v>200</v>
+      </c>
+      <c r="J45" s="3">
+        <v>100</v>
+      </c>
+      <c r="K45" s="3">
+        <v>200</v>
+      </c>
+      <c r="L45" s="3">
         <v>400</v>
       </c>
-      <c r="H45" s="3">
-        <v>200</v>
-      </c>
-      <c r="I45" s="3">
-        <v>100</v>
-      </c>
-      <c r="J45" s="3">
-        <v>200</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
+        <v>600</v>
+      </c>
+      <c r="N45" s="3">
         <v>400</v>
       </c>
-      <c r="L45" s="3">
-        <v>600</v>
-      </c>
-      <c r="M45" s="3">
-        <v>400</v>
-      </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>7700</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>264400</v>
+        <v>1122300</v>
       </c>
       <c r="E46" s="3">
-        <v>128400</v>
+        <v>247700</v>
       </c>
       <c r="F46" s="3">
-        <v>88600</v>
+        <v>120300</v>
       </c>
       <c r="G46" s="3">
-        <v>90500</v>
+        <v>83000</v>
       </c>
       <c r="H46" s="3">
-        <v>70600</v>
+        <v>84800</v>
       </c>
       <c r="I46" s="3">
-        <v>61400</v>
+        <v>66100</v>
       </c>
       <c r="J46" s="3">
+        <v>57500</v>
+      </c>
+      <c r="K46" s="3">
         <v>25700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>41800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>43700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>43900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>35200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>49700</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>206600</v>
+        <v>609000</v>
       </c>
       <c r="E47" s="3">
-        <v>107300</v>
+        <v>193600</v>
       </c>
       <c r="F47" s="3">
-        <v>65700</v>
+        <v>100600</v>
       </c>
       <c r="G47" s="3">
-        <v>41100</v>
+        <v>61600</v>
       </c>
       <c r="H47" s="3">
-        <v>31100</v>
+        <v>38600</v>
       </c>
       <c r="I47" s="3">
-        <v>22700</v>
+        <v>29100</v>
       </c>
       <c r="J47" s="3">
+        <v>21200</v>
+      </c>
+      <c r="K47" s="3">
         <v>10800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>17900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>22600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>13900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>25600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>41700</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>427300</v>
+        <v>2157200</v>
       </c>
       <c r="E48" s="3">
-        <v>190500</v>
+        <v>400400</v>
       </c>
       <c r="F48" s="3">
-        <v>151300</v>
+        <v>178500</v>
       </c>
       <c r="G48" s="3">
-        <v>234200</v>
+        <v>141800</v>
       </c>
       <c r="H48" s="3">
-        <v>153800</v>
+        <v>219400</v>
       </c>
       <c r="I48" s="3">
-        <v>123800</v>
+        <v>144100</v>
       </c>
       <c r="J48" s="3">
+        <v>116000</v>
+      </c>
+      <c r="K48" s="3">
         <v>45600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>62500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>91500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>85200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>199100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>329000</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>27000</v>
+        <v>81000</v>
       </c>
       <c r="E49" s="3">
-        <v>4400</v>
+        <v>25300</v>
       </c>
       <c r="F49" s="3">
-        <v>3800</v>
+        <v>4100</v>
       </c>
       <c r="G49" s="3">
-        <v>10100</v>
+        <v>3600</v>
       </c>
       <c r="H49" s="3">
-        <v>7500</v>
+        <v>9400</v>
       </c>
       <c r="I49" s="3">
-        <v>7100</v>
+        <v>7000</v>
       </c>
       <c r="J49" s="3">
+        <v>6600</v>
+      </c>
+      <c r="K49" s="3">
         <v>2200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>11100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>59600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>91000</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>7100</v>
+        <v>400</v>
       </c>
       <c r="E52" s="3">
-        <v>9700</v>
+        <v>6700</v>
       </c>
       <c r="F52" s="3">
-        <v>147300</v>
+        <v>9100</v>
       </c>
       <c r="G52" s="3">
-        <v>1900</v>
+        <v>138100</v>
       </c>
       <c r="H52" s="3">
+        <v>1800</v>
+      </c>
+      <c r="I52" s="3">
         <v>100</v>
       </c>
-      <c r="I52" s="3">
-        <v>22600</v>
-      </c>
       <c r="J52" s="3">
+        <v>21200</v>
+      </c>
+      <c r="K52" s="3">
         <v>1400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>200</v>
-      </c>
-      <c r="L52" s="3">
-        <v>900</v>
       </c>
       <c r="M52" s="3">
         <v>900</v>
       </c>
       <c r="N52" s="3">
+        <v>900</v>
+      </c>
+      <c r="O52" s="3">
         <v>12300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>81600</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>932500</v>
+        <v>3969900</v>
       </c>
       <c r="E54" s="3">
-        <v>440300</v>
+        <v>873700</v>
       </c>
       <c r="F54" s="3">
-        <v>456800</v>
+        <v>412500</v>
       </c>
       <c r="G54" s="3">
-        <v>377900</v>
+        <v>428000</v>
       </c>
       <c r="H54" s="3">
-        <v>263100</v>
+        <v>354000</v>
       </c>
       <c r="I54" s="3">
-        <v>236700</v>
+        <v>246500</v>
       </c>
       <c r="J54" s="3">
+        <v>221800</v>
+      </c>
+      <c r="K54" s="3">
         <v>85800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>125600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>167300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>155000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>187100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>316500</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,260 +2654,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>41800</v>
+        <v>168700</v>
       </c>
       <c r="E57" s="3">
-        <v>19200</v>
+        <v>39100</v>
       </c>
       <c r="F57" s="3">
-        <v>9100</v>
+        <v>18000</v>
       </c>
       <c r="G57" s="3">
-        <v>25100</v>
+        <v>8500</v>
       </c>
       <c r="H57" s="3">
-        <v>26600</v>
+        <v>23500</v>
       </c>
       <c r="I57" s="3">
-        <v>26900</v>
+        <v>24900</v>
       </c>
       <c r="J57" s="3">
+        <v>25200</v>
+      </c>
+      <c r="K57" s="3">
         <v>14000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>28500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>45000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>38100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>52600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>25300</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>54000</v>
+        <v>191700</v>
       </c>
       <c r="E58" s="3">
-        <v>9500</v>
+        <v>50600</v>
       </c>
       <c r="F58" s="3">
-        <v>22600</v>
+        <v>8900</v>
       </c>
       <c r="G58" s="3">
-        <v>12200</v>
+        <v>21200</v>
       </c>
       <c r="H58" s="3">
-        <v>15900</v>
+        <v>11400</v>
       </c>
       <c r="I58" s="3">
-        <v>9600</v>
+        <v>14900</v>
       </c>
       <c r="J58" s="3">
+        <v>9000</v>
+      </c>
+      <c r="K58" s="3">
         <v>11900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>7800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>9300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>13100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>47000</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>28200</v>
+        <v>78200</v>
       </c>
       <c r="E59" s="3">
-        <v>10200</v>
+        <v>26500</v>
       </c>
       <c r="F59" s="3">
-        <v>10100</v>
+        <v>9600</v>
       </c>
       <c r="G59" s="3">
-        <v>19500</v>
+        <v>9500</v>
       </c>
       <c r="H59" s="3">
-        <v>12400</v>
+        <v>18200</v>
       </c>
       <c r="I59" s="3">
-        <v>12600</v>
+        <v>11600</v>
       </c>
       <c r="J59" s="3">
+        <v>11800</v>
+      </c>
+      <c r="K59" s="3">
         <v>7600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>15200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>24200</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>124000</v>
+        <v>438500</v>
       </c>
       <c r="E60" s="3">
-        <v>39000</v>
+        <v>116200</v>
       </c>
       <c r="F60" s="3">
-        <v>41900</v>
+        <v>36500</v>
       </c>
       <c r="G60" s="3">
-        <v>56700</v>
+        <v>39200</v>
       </c>
       <c r="H60" s="3">
-        <v>54900</v>
+        <v>53200</v>
       </c>
       <c r="I60" s="3">
-        <v>49100</v>
+        <v>51400</v>
       </c>
       <c r="J60" s="3">
+        <v>46000</v>
+      </c>
+      <c r="K60" s="3">
         <v>33400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>41300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>63300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>56900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>53000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>66100</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>265500</v>
+        <v>1040900</v>
       </c>
       <c r="E61" s="3">
-        <v>156000</v>
+        <v>248800</v>
       </c>
       <c r="F61" s="3">
-        <v>128100</v>
+        <v>146200</v>
       </c>
       <c r="G61" s="3">
-        <v>117200</v>
+        <v>120000</v>
       </c>
       <c r="H61" s="3">
-        <v>85100</v>
+        <v>109900</v>
       </c>
       <c r="I61" s="3">
-        <v>60800</v>
+        <v>79800</v>
       </c>
       <c r="J61" s="3">
+        <v>57000</v>
+      </c>
+      <c r="K61" s="3">
         <v>17000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>28800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>37600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>36100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>36700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>65100</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>93800</v>
+        <v>461700</v>
       </c>
       <c r="E62" s="3">
+        <v>87900</v>
+      </c>
+      <c r="F62" s="3">
+        <v>38400</v>
+      </c>
+      <c r="G62" s="3">
+        <v>24500</v>
+      </c>
+      <c r="H62" s="3">
         <v>41000</v>
       </c>
-      <c r="F62" s="3">
-        <v>26200</v>
-      </c>
-      <c r="G62" s="3">
-        <v>43800</v>
-      </c>
-      <c r="H62" s="3">
-        <v>39800</v>
-      </c>
       <c r="I62" s="3">
-        <v>40400</v>
+        <v>37300</v>
       </c>
       <c r="J62" s="3">
+        <v>37900</v>
+      </c>
+      <c r="K62" s="3">
         <v>19800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>19400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>31200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>26500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>90700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>73600</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>484600</v>
+        <v>1948400</v>
       </c>
       <c r="E66" s="3">
-        <v>236700</v>
+        <v>454100</v>
       </c>
       <c r="F66" s="3">
-        <v>323300</v>
+        <v>221800</v>
       </c>
       <c r="G66" s="3">
-        <v>250400</v>
+        <v>302900</v>
       </c>
       <c r="H66" s="3">
-        <v>199700</v>
+        <v>234600</v>
       </c>
       <c r="I66" s="3">
-        <v>174000</v>
+        <v>187100</v>
       </c>
       <c r="J66" s="3">
+        <v>163000</v>
+      </c>
+      <c r="K66" s="3">
         <v>73500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>95500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>138300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>129100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>157300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>252600</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3088,9 +3255,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>292400</v>
+        <v>1430800</v>
       </c>
       <c r="E72" s="3">
-        <v>115000</v>
+        <v>274000</v>
       </c>
       <c r="F72" s="3">
-        <v>68800</v>
+        <v>107800</v>
       </c>
       <c r="G72" s="3">
-        <v>78300</v>
+        <v>64500</v>
       </c>
       <c r="H72" s="3">
-        <v>28300</v>
+        <v>73400</v>
       </c>
       <c r="I72" s="3">
-        <v>28300</v>
+        <v>26500</v>
       </c>
       <c r="J72" s="3">
+        <v>26500</v>
+      </c>
+      <c r="K72" s="3">
         <v>4500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>17600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>12800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-8600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-10400</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>447800</v>
+        <v>2021500</v>
       </c>
       <c r="E76" s="3">
-        <v>203600</v>
+        <v>419600</v>
       </c>
       <c r="F76" s="3">
-        <v>133500</v>
+        <v>190800</v>
       </c>
       <c r="G76" s="3">
-        <v>127500</v>
+        <v>125100</v>
       </c>
       <c r="H76" s="3">
-        <v>63400</v>
+        <v>119500</v>
       </c>
       <c r="I76" s="3">
-        <v>62700</v>
+        <v>59400</v>
       </c>
       <c r="J76" s="3">
+        <v>58700</v>
+      </c>
+      <c r="K76" s="3">
         <v>12300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>30100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>29000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>25900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>29800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>63900</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>72000</v>
+        <v>35900</v>
       </c>
       <c r="E81" s="3">
-        <v>30100</v>
+        <v>67500</v>
       </c>
       <c r="F81" s="3">
-        <v>-34900</v>
+        <v>28200</v>
       </c>
       <c r="G81" s="3">
-        <v>36600</v>
+        <v>-32700</v>
       </c>
       <c r="H81" s="3">
-        <v>9400</v>
+        <v>34300</v>
       </c>
       <c r="I81" s="3">
-        <v>12000</v>
+        <v>8800</v>
       </c>
       <c r="J81" s="3">
-        <v>0</v>
+        <v>11200</v>
       </c>
       <c r="K81" s="3">
+        <v>0</v>
+      </c>
+      <c r="L81" s="3">
         <v>13200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>7400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-10700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>900</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,50 +3687,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>30800</v>
+        <v>82700</v>
       </c>
       <c r="E83" s="3">
-        <v>21800</v>
+        <v>28800</v>
       </c>
       <c r="F83" s="3">
-        <v>16100</v>
+        <v>20500</v>
       </c>
       <c r="G83" s="3">
-        <v>15500</v>
+        <v>15100</v>
       </c>
       <c r="H83" s="3">
-        <v>9800</v>
+        <v>14500</v>
       </c>
       <c r="I83" s="3">
-        <v>8600</v>
+        <v>9200</v>
       </c>
       <c r="J83" s="3">
+        <v>8000</v>
+      </c>
+      <c r="K83" s="3">
         <v>2400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3100</v>
-      </c>
-      <c r="L83" s="3">
-        <v>4600</v>
       </c>
       <c r="M83" s="3">
         <v>4600</v>
       </c>
       <c r="N83" s="3">
+        <v>4600</v>
+      </c>
+      <c r="O83" s="3">
         <v>6200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>10200</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>90100</v>
+        <v>184200</v>
       </c>
       <c r="E89" s="3">
-        <v>84800</v>
+        <v>84400</v>
       </c>
       <c r="F89" s="3">
-        <v>52500</v>
+        <v>79400</v>
       </c>
       <c r="G89" s="3">
-        <v>41800</v>
+        <v>49200</v>
       </c>
       <c r="H89" s="3">
-        <v>25400</v>
+        <v>39200</v>
       </c>
       <c r="I89" s="3">
-        <v>17800</v>
+        <v>23800</v>
       </c>
       <c r="J89" s="3">
+        <v>16600</v>
+      </c>
+      <c r="K89" s="3">
         <v>6600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>18800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>25500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>22200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>19800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>29800</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,50 +4021,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-57600</v>
+        <v>-202000</v>
       </c>
       <c r="E91" s="3">
-        <v>-21700</v>
+        <v>-54000</v>
       </c>
       <c r="F91" s="3">
-        <v>-9300</v>
+        <v>-20300</v>
       </c>
       <c r="G91" s="3">
-        <v>-32000</v>
+        <v>-8700</v>
       </c>
       <c r="H91" s="3">
-        <v>-28200</v>
+        <v>-30000</v>
       </c>
       <c r="I91" s="3">
-        <v>-20300</v>
+        <v>-26400</v>
       </c>
       <c r="J91" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="K91" s="3">
         <v>-6900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-20700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-23100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-14800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-11300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-42800</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-83300</v>
+        <v>-78400</v>
       </c>
       <c r="E94" s="3">
-        <v>-50800</v>
+        <v>-78100</v>
       </c>
       <c r="F94" s="3">
-        <v>-17200</v>
+        <v>-47600</v>
       </c>
       <c r="G94" s="3">
-        <v>-19100</v>
+        <v>-16200</v>
       </c>
       <c r="H94" s="3">
+        <v>-17900</v>
+      </c>
+      <c r="I94" s="3">
         <v>800</v>
       </c>
-      <c r="I94" s="3">
-        <v>-35500</v>
-      </c>
       <c r="J94" s="3">
+        <v>-33200</v>
+      </c>
+      <c r="K94" s="3">
         <v>-12500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-30700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-24500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-19400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-14900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-44900</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,22 +4220,23 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>-700</v>
+        <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>-100</v>
+        <v>-600</v>
       </c>
       <c r="H96" s="3">
         <v>-100</v>
@@ -4012,26 +4245,29 @@
         <v>-100</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-100</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-200</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-500</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,133 +4397,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-5600</v>
+        <v>-55200</v>
       </c>
       <c r="E100" s="3">
-        <v>-35300</v>
+        <v>-5300</v>
       </c>
       <c r="F100" s="3">
-        <v>-33300</v>
+        <v>-33100</v>
       </c>
       <c r="G100" s="3">
-        <v>-23500</v>
+        <v>-31200</v>
       </c>
       <c r="H100" s="3">
-        <v>-19700</v>
+        <v>-22000</v>
       </c>
       <c r="I100" s="3">
-        <v>15500</v>
+        <v>-18400</v>
       </c>
       <c r="J100" s="3">
+        <v>14600</v>
+      </c>
+      <c r="K100" s="3">
         <v>6500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>12300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-9000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>10300</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>7100</v>
+        <v>73400</v>
       </c>
       <c r="E101" s="3">
+        <v>6700</v>
+      </c>
+      <c r="F101" s="3">
+        <v>600</v>
+      </c>
+      <c r="G101" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="H101" s="3">
+        <v>5300</v>
+      </c>
+      <c r="I101" s="3">
+        <v>2100</v>
+      </c>
+      <c r="J101" s="3">
+        <v>500</v>
+      </c>
+      <c r="K101" s="3">
+        <v>400</v>
+      </c>
+      <c r="L101" s="3">
+        <v>300</v>
+      </c>
+      <c r="M101" s="3">
+        <v>400</v>
+      </c>
+      <c r="N101" s="3">
+        <v>600</v>
+      </c>
+      <c r="O101" s="3">
         <v>700</v>
       </c>
-      <c r="F101" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="G101" s="3">
-        <v>5600</v>
-      </c>
-      <c r="H101" s="3">
-        <v>2200</v>
-      </c>
-      <c r="I101" s="3">
-        <v>600</v>
-      </c>
-      <c r="J101" s="3">
-        <v>400</v>
-      </c>
-      <c r="K101" s="3">
-        <v>300</v>
-      </c>
-      <c r="L101" s="3">
-        <v>400</v>
-      </c>
-      <c r="M101" s="3">
-        <v>600</v>
-      </c>
-      <c r="N101" s="3">
-        <v>700</v>
-      </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>2700</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>8300</v>
+        <v>124000</v>
       </c>
       <c r="E102" s="3">
-        <v>-700</v>
+        <v>7800</v>
       </c>
       <c r="F102" s="3">
-        <v>-1800</v>
+        <v>-600</v>
       </c>
       <c r="G102" s="3">
-        <v>4900</v>
+        <v>-1700</v>
       </c>
       <c r="H102" s="3">
-        <v>8800</v>
+        <v>4600</v>
       </c>
       <c r="I102" s="3">
-        <v>-1600</v>
+        <v>8200</v>
       </c>
       <c r="J102" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="K102" s="3">
         <v>1000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2100</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/PAM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PAM_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="92">
   <si>
     <t>PAM</t>
   </si>
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>534300</v>
+        <v>1732000</v>
       </c>
       <c r="E8" s="3">
-        <v>251900</v>
+        <v>1829000</v>
       </c>
       <c r="F8" s="3">
-        <v>150400</v>
+        <v>1508000</v>
       </c>
       <c r="G8" s="3">
-        <v>79800</v>
+        <v>1073000</v>
       </c>
       <c r="H8" s="3">
-        <v>67300</v>
+        <v>1340000</v>
       </c>
       <c r="I8" s="3">
-        <v>56300</v>
+        <v>1436000</v>
       </c>
       <c r="J8" s="3">
-        <v>85300</v>
+        <v>4379800</v>
       </c>
       <c r="K8" s="3">
         <v>27900</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>333400</v>
+        <v>1112000</v>
       </c>
       <c r="E9" s="3">
-        <v>157300</v>
+        <v>1143000</v>
       </c>
       <c r="F9" s="3">
-        <v>95100</v>
+        <v>953000</v>
       </c>
       <c r="G9" s="3">
-        <v>49200</v>
+        <v>664000</v>
       </c>
       <c r="H9" s="3">
-        <v>40800</v>
+        <v>812000</v>
       </c>
       <c r="I9" s="3">
-        <v>32600</v>
+        <v>833000</v>
       </c>
       <c r="J9" s="3">
-        <v>62300</v>
+        <v>3173300</v>
       </c>
       <c r="K9" s="3">
         <v>20300</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>200900</v>
+        <v>620000</v>
       </c>
       <c r="E10" s="3">
-        <v>94600</v>
+        <v>686000</v>
       </c>
       <c r="F10" s="3">
-        <v>55300</v>
+        <v>555000</v>
       </c>
       <c r="G10" s="3">
-        <v>30600</v>
+        <v>409000</v>
       </c>
       <c r="H10" s="3">
-        <v>26500</v>
+        <v>528000</v>
       </c>
       <c r="I10" s="3">
-        <v>23700</v>
+        <v>603000</v>
       </c>
       <c r="J10" s="3">
-        <v>22900</v>
+        <v>1206600</v>
       </c>
       <c r="K10" s="3">
         <v>7600</v>
@@ -879,26 +879,26 @@
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
-        <v>1900</v>
-      </c>
-      <c r="E12" s="3">
-        <v>100</v>
-      </c>
-      <c r="F12" s="3">
-        <v>100</v>
-      </c>
-      <c r="G12" s="3">
-        <v>0</v>
-      </c>
-      <c r="H12" s="3">
-        <v>500</v>
-      </c>
-      <c r="I12" s="3">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3">
-        <v>100</v>
+      <c r="D12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K12" s="3">
         <v>100</v>
@@ -970,25 +970,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>32400</v>
+        <v>34000</v>
       </c>
       <c r="E14" s="3">
-        <v>7000</v>
+        <v>16000</v>
       </c>
       <c r="F14" s="3">
-        <v>2300</v>
+        <v>-16000</v>
       </c>
       <c r="G14" s="3">
-        <v>11900</v>
+        <v>96000</v>
       </c>
       <c r="H14" s="3">
-        <v>5600</v>
+        <v>37000</v>
       </c>
       <c r="I14" s="3">
-        <v>-13900</v>
+        <v>-14000</v>
       </c>
       <c r="J14" s="3">
-        <v>-10800</v>
+        <v>37200</v>
       </c>
       <c r="K14" s="3">
         <v>6200</v>
@@ -1015,25 +1015,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2300</v>
+        <v>267000</v>
       </c>
       <c r="E15" s="3">
-        <v>800</v>
+        <v>212000</v>
       </c>
       <c r="F15" s="3">
-        <v>500</v>
+        <v>205000</v>
       </c>
       <c r="G15" s="3">
-        <v>400</v>
+        <v>204000</v>
       </c>
       <c r="H15" s="3">
-        <v>500</v>
+        <v>184000</v>
       </c>
       <c r="I15" s="3">
-        <v>200</v>
+        <v>165000</v>
       </c>
       <c r="J15" s="3">
-        <v>400</v>
+        <v>413300</v>
       </c>
       <c r="K15" s="3">
         <v>100</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>411800</v>
+        <v>1341000</v>
       </c>
       <c r="E17" s="3">
-        <v>159900</v>
+        <v>1322000</v>
       </c>
       <c r="F17" s="3">
-        <v>91700</v>
+        <v>1072000</v>
       </c>
       <c r="G17" s="3">
-        <v>60900</v>
+        <v>812000</v>
       </c>
       <c r="H17" s="3">
-        <v>44100</v>
+        <v>970000</v>
       </c>
       <c r="I17" s="3">
-        <v>16200</v>
+        <v>1000000</v>
       </c>
       <c r="J17" s="3">
-        <v>58900</v>
+        <v>3701700</v>
       </c>
       <c r="K17" s="3">
         <v>25700</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>122500</v>
+        <v>391000</v>
       </c>
       <c r="E18" s="3">
-        <v>92000</v>
+        <v>507000</v>
       </c>
       <c r="F18" s="3">
-        <v>58700</v>
+        <v>436000</v>
       </c>
       <c r="G18" s="3">
-        <v>18900</v>
+        <v>261000</v>
       </c>
       <c r="H18" s="3">
-        <v>23200</v>
+        <v>370000</v>
       </c>
       <c r="I18" s="3">
-        <v>40100</v>
+        <v>436000</v>
       </c>
       <c r="J18" s="3">
-        <v>26400</v>
+        <v>678100</v>
       </c>
       <c r="K18" s="3">
         <v>2200</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>145400</v>
+        <v>-547000</v>
       </c>
       <c r="E20" s="3">
-        <v>20200</v>
+        <v>-274000</v>
       </c>
       <c r="F20" s="3">
-        <v>-5500</v>
+        <v>-79000</v>
       </c>
       <c r="G20" s="3">
-        <v>6200</v>
+        <v>-124000</v>
       </c>
       <c r="H20" s="3">
-        <v>9000</v>
+        <v>-247000</v>
       </c>
       <c r="I20" s="3">
-        <v>-31600</v>
+        <v>294000</v>
       </c>
       <c r="J20" s="3">
-        <v>-4200</v>
+        <v>-499600</v>
       </c>
       <c r="K20" s="3">
         <v>-500</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>350500</v>
+        <v>1205000</v>
       </c>
       <c r="E21" s="3">
-        <v>141000</v>
+        <v>993000</v>
       </c>
       <c r="F21" s="3">
-        <v>73600</v>
+        <v>720000</v>
       </c>
       <c r="G21" s="3">
-        <v>40200</v>
+        <v>589000</v>
       </c>
       <c r="H21" s="3">
-        <v>46600</v>
+        <v>801000</v>
       </c>
       <c r="I21" s="3">
-        <v>17700</v>
+        <v>307000</v>
       </c>
       <c r="J21" s="3">
-        <v>30200</v>
+        <v>1591100</v>
       </c>
       <c r="K21" s="3">
         <v>4200</v>
@@ -1275,25 +1275,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>91800</v>
+        <v>356000</v>
       </c>
       <c r="E22" s="3">
-        <v>24500</v>
+        <v>216000</v>
       </c>
       <c r="F22" s="3">
-        <v>13400</v>
+        <v>178000</v>
       </c>
       <c r="G22" s="3">
-        <v>12100</v>
+        <v>170000</v>
       </c>
       <c r="H22" s="3">
-        <v>8300</v>
+        <v>183000</v>
       </c>
       <c r="I22" s="3">
-        <v>6200</v>
+        <v>179000</v>
       </c>
       <c r="J22" s="3">
-        <v>6400</v>
+        <v>458700</v>
       </c>
       <c r="K22" s="3">
         <v>3400</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>176000</v>
+        <v>623000</v>
       </c>
       <c r="E23" s="3">
-        <v>87700</v>
+        <v>581000</v>
       </c>
       <c r="F23" s="3">
-        <v>39700</v>
+        <v>390000</v>
       </c>
       <c r="G23" s="3">
-        <v>13000</v>
+        <v>159000</v>
       </c>
       <c r="H23" s="3">
-        <v>23900</v>
+        <v>473000</v>
       </c>
       <c r="I23" s="3">
-        <v>2300</v>
+        <v>59000</v>
       </c>
       <c r="J23" s="3">
-        <v>15800</v>
+        <v>809500</v>
       </c>
       <c r="K23" s="3">
         <v>-1700</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>137900</v>
+        <v>318000</v>
       </c>
       <c r="E24" s="3">
-        <v>20200</v>
+        <v>124000</v>
       </c>
       <c r="F24" s="3">
-        <v>7600</v>
+        <v>77000</v>
       </c>
       <c r="G24" s="3">
-        <v>3200</v>
+        <v>35000</v>
       </c>
       <c r="H24" s="3">
-        <v>-4700</v>
+        <v>-130000</v>
       </c>
       <c r="I24" s="3">
-        <v>-1300</v>
+        <v>-32000</v>
       </c>
       <c r="J24" s="3">
-        <v>-1000</v>
+        <v>-52600</v>
       </c>
       <c r="K24" s="3">
         <v>-1300</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>38200</v>
+        <v>305000</v>
       </c>
       <c r="E26" s="3">
-        <v>67500</v>
+        <v>457000</v>
       </c>
       <c r="F26" s="3">
-        <v>32200</v>
+        <v>313000</v>
       </c>
       <c r="G26" s="3">
-        <v>9700</v>
+        <v>124000</v>
       </c>
       <c r="H26" s="3">
-        <v>28600</v>
+        <v>603000</v>
       </c>
       <c r="I26" s="3">
-        <v>3600</v>
+        <v>91000</v>
       </c>
       <c r="J26" s="3">
-        <v>16800</v>
+        <v>862100</v>
       </c>
       <c r="K26" s="3">
         <v>-400</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>35900</v>
+        <v>302000</v>
       </c>
       <c r="E27" s="3">
-        <v>67500</v>
+        <v>456000</v>
       </c>
       <c r="F27" s="3">
-        <v>35600</v>
+        <v>273000</v>
       </c>
       <c r="G27" s="3">
-        <v>18600</v>
+        <v>-367000</v>
       </c>
       <c r="H27" s="3">
-        <v>22000</v>
+        <v>692000</v>
       </c>
       <c r="I27" s="3">
-        <v>1100</v>
+        <v>224000</v>
       </c>
       <c r="J27" s="3">
-        <v>13200</v>
+        <v>576800</v>
       </c>
       <c r="K27" s="3">
         <v>-100</v>
@@ -1596,19 +1596,19 @@
         <v>0</v>
       </c>
       <c r="F29" s="3">
-        <v>-7400</v>
+        <v>-75000</v>
       </c>
       <c r="G29" s="3">
-        <v>-51300</v>
+        <v>-592000</v>
       </c>
       <c r="H29" s="3">
-        <v>12300</v>
+        <v>197000</v>
       </c>
       <c r="I29" s="3">
-        <v>7700</v>
+        <v>196000</v>
       </c>
       <c r="J29" s="3">
-        <v>-2000</v>
+        <v>-101100</v>
       </c>
       <c r="K29" s="3">
         <v>100</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-145400</v>
+        <v>547000</v>
       </c>
       <c r="E32" s="3">
-        <v>-20200</v>
+        <v>274000</v>
       </c>
       <c r="F32" s="3">
-        <v>5500</v>
+        <v>79000</v>
       </c>
       <c r="G32" s="3">
-        <v>-6200</v>
+        <v>124000</v>
       </c>
       <c r="H32" s="3">
-        <v>-9000</v>
+        <v>247000</v>
       </c>
       <c r="I32" s="3">
-        <v>31600</v>
+        <v>-294000</v>
       </c>
       <c r="J32" s="3">
-        <v>4200</v>
+        <v>499600</v>
       </c>
       <c r="K32" s="3">
         <v>500</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>35900</v>
+        <v>302000</v>
       </c>
       <c r="E33" s="3">
-        <v>67500</v>
+        <v>456000</v>
       </c>
       <c r="F33" s="3">
-        <v>28200</v>
+        <v>273000</v>
       </c>
       <c r="G33" s="3">
-        <v>-32700</v>
+        <v>-367000</v>
       </c>
       <c r="H33" s="3">
-        <v>34300</v>
+        <v>692000</v>
       </c>
       <c r="I33" s="3">
-        <v>8800</v>
+        <v>224000</v>
       </c>
       <c r="J33" s="3">
-        <v>11200</v>
+        <v>576700</v>
       </c>
       <c r="K33" s="3">
         <v>0</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>35900</v>
+        <v>302000</v>
       </c>
       <c r="E35" s="3">
-        <v>67500</v>
+        <v>456000</v>
       </c>
       <c r="F35" s="3">
-        <v>28200</v>
+        <v>273000</v>
       </c>
       <c r="G35" s="3">
-        <v>-32700</v>
+        <v>-367000</v>
       </c>
       <c r="H35" s="3">
-        <v>34300</v>
+        <v>692000</v>
       </c>
       <c r="I35" s="3">
-        <v>8800</v>
+        <v>224000</v>
       </c>
       <c r="J35" s="3">
-        <v>11200</v>
+        <v>576700</v>
       </c>
       <c r="K35" s="3">
         <v>0</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>143500</v>
+        <v>171000</v>
       </c>
       <c r="E41" s="3">
-        <v>19500</v>
+        <v>106000</v>
       </c>
       <c r="F41" s="3">
-        <v>11700</v>
+        <v>110000</v>
       </c>
       <c r="G41" s="3">
-        <v>12400</v>
+        <v>141000</v>
       </c>
       <c r="H41" s="3">
-        <v>14000</v>
+        <v>225000</v>
       </c>
       <c r="I41" s="3">
-        <v>10500</v>
+        <v>241600</v>
       </c>
       <c r="J41" s="3">
-        <v>1200</v>
+        <v>63000</v>
       </c>
       <c r="K41" s="3">
         <v>1600</v>
@@ -2038,25 +2038,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>558100</v>
+        <v>664000</v>
       </c>
       <c r="E42" s="3">
-        <v>109400</v>
+        <v>594000</v>
       </c>
       <c r="F42" s="3">
-        <v>49500</v>
+        <v>463000</v>
       </c>
       <c r="G42" s="3">
-        <v>30600</v>
+        <v>350000</v>
       </c>
       <c r="H42" s="3">
-        <v>26100</v>
+        <v>419000</v>
       </c>
       <c r="I42" s="3">
-        <v>19100</v>
+        <v>441000</v>
       </c>
       <c r="J42" s="3">
-        <v>22500</v>
+        <v>1154300</v>
       </c>
       <c r="K42" s="3">
         <v>4700</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>243400</v>
+        <v>262000</v>
       </c>
       <c r="E43" s="3">
-        <v>84000</v>
+        <v>429000</v>
       </c>
       <c r="F43" s="3">
-        <v>41400</v>
+        <v>357000</v>
       </c>
       <c r="G43" s="3">
-        <v>29500</v>
+        <v>331000</v>
       </c>
       <c r="H43" s="3">
-        <v>34800</v>
+        <v>554000</v>
       </c>
       <c r="I43" s="3">
-        <v>30400</v>
+        <v>686900</v>
       </c>
       <c r="J43" s="3">
-        <v>29300</v>
+        <v>1418300</v>
       </c>
       <c r="K43" s="3">
         <v>15500</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>172700</v>
+        <v>205000</v>
       </c>
       <c r="E44" s="3">
-        <v>32000</v>
+        <v>173000</v>
       </c>
       <c r="F44" s="3">
-        <v>16500</v>
+        <v>155000</v>
       </c>
       <c r="G44" s="3">
-        <v>10200</v>
+        <v>116000</v>
       </c>
       <c r="H44" s="3">
-        <v>9500</v>
+        <v>153000</v>
       </c>
       <c r="I44" s="3">
-        <v>6000</v>
+        <v>137300</v>
       </c>
       <c r="J44" s="3">
-        <v>4400</v>
+        <v>227800</v>
       </c>
       <c r="K44" s="3">
         <v>3700</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>4700</v>
+        <v>29000</v>
       </c>
       <c r="E45" s="3">
-        <v>2800</v>
+        <v>27000</v>
       </c>
       <c r="F45" s="3">
-        <v>1100</v>
+        <v>30000</v>
       </c>
       <c r="G45" s="3">
-        <v>300</v>
+        <v>1475000</v>
       </c>
       <c r="H45" s="3">
-        <v>400</v>
+        <v>9000</v>
       </c>
       <c r="I45" s="3">
-        <v>200</v>
+        <v>15100</v>
       </c>
       <c r="J45" s="3">
-        <v>100</v>
+        <v>1071900</v>
       </c>
       <c r="K45" s="3">
         <v>200</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1122300</v>
+        <v>1336000</v>
       </c>
       <c r="E46" s="3">
-        <v>247700</v>
+        <v>1343000</v>
       </c>
       <c r="F46" s="3">
-        <v>120300</v>
+        <v>1125000</v>
       </c>
       <c r="G46" s="3">
-        <v>83000</v>
+        <v>2417000</v>
       </c>
       <c r="H46" s="3">
-        <v>84800</v>
+        <v>1362000</v>
       </c>
       <c r="I46" s="3">
-        <v>66100</v>
+        <v>1523500</v>
       </c>
       <c r="J46" s="3">
-        <v>57500</v>
+        <v>3940800</v>
       </c>
       <c r="K46" s="3">
         <v>25700</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>609000</v>
+        <v>707000</v>
       </c>
       <c r="E47" s="3">
-        <v>193600</v>
+        <v>1031000</v>
       </c>
       <c r="F47" s="3">
-        <v>100600</v>
+        <v>908000</v>
       </c>
       <c r="G47" s="3">
-        <v>61600</v>
+        <v>660000</v>
       </c>
       <c r="H47" s="3">
-        <v>38600</v>
+        <v>540000</v>
       </c>
       <c r="I47" s="3">
-        <v>29100</v>
+        <v>418500</v>
       </c>
       <c r="J47" s="3">
-        <v>21200</v>
+        <v>649500</v>
       </c>
       <c r="K47" s="3">
         <v>10800</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2157200</v>
+        <v>2501000</v>
       </c>
       <c r="E48" s="3">
-        <v>400400</v>
+        <v>2130000</v>
       </c>
       <c r="F48" s="3">
-        <v>178500</v>
+        <v>1619000</v>
       </c>
       <c r="G48" s="3">
-        <v>141800</v>
+        <v>1606000</v>
       </c>
       <c r="H48" s="3">
-        <v>219400</v>
+        <v>3505000</v>
       </c>
       <c r="I48" s="3">
-        <v>144100</v>
+        <v>3301000</v>
       </c>
       <c r="J48" s="3">
-        <v>116000</v>
+        <v>5901000</v>
       </c>
       <c r="K48" s="3">
         <v>45600</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>81000</v>
+        <v>96000</v>
       </c>
       <c r="E49" s="3">
-        <v>25300</v>
+        <v>138000</v>
       </c>
       <c r="F49" s="3">
-        <v>4100</v>
+        <v>38000</v>
       </c>
       <c r="G49" s="3">
-        <v>3600</v>
+        <v>41000</v>
       </c>
       <c r="H49" s="3">
-        <v>9400</v>
+        <v>151000</v>
       </c>
       <c r="I49" s="3">
-        <v>7000</v>
+        <v>161500</v>
       </c>
       <c r="J49" s="3">
-        <v>6600</v>
+        <v>339400</v>
       </c>
       <c r="K49" s="3">
         <v>2200</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>400</v>
+        <v>82000</v>
       </c>
       <c r="E52" s="3">
-        <v>6700</v>
+        <v>64000</v>
       </c>
       <c r="F52" s="3">
-        <v>9100</v>
+        <v>87000</v>
       </c>
       <c r="G52" s="3">
-        <v>138100</v>
+        <v>58000</v>
       </c>
       <c r="H52" s="3">
-        <v>1800</v>
+        <v>90000</v>
       </c>
       <c r="I52" s="3">
-        <v>100</v>
+        <v>180000</v>
       </c>
       <c r="J52" s="3">
-        <v>21200</v>
+        <v>229200</v>
       </c>
       <c r="K52" s="3">
         <v>1400</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>3969900</v>
+        <v>4722000</v>
       </c>
       <c r="E54" s="3">
-        <v>873700</v>
+        <v>4742000</v>
       </c>
       <c r="F54" s="3">
-        <v>412500</v>
+        <v>3861000</v>
       </c>
       <c r="G54" s="3">
-        <v>428000</v>
+        <v>4890000</v>
       </c>
       <c r="H54" s="3">
-        <v>354000</v>
+        <v>5684000</v>
       </c>
       <c r="I54" s="3">
-        <v>246500</v>
+        <v>5679500</v>
       </c>
       <c r="J54" s="3">
-        <v>221800</v>
+        <v>11389400</v>
       </c>
       <c r="K54" s="3">
         <v>85800</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>168700</v>
+        <v>201000</v>
       </c>
       <c r="E57" s="3">
-        <v>39100</v>
+        <v>212000</v>
       </c>
       <c r="F57" s="3">
-        <v>18000</v>
+        <v>169000</v>
       </c>
       <c r="G57" s="3">
-        <v>8500</v>
+        <v>97000</v>
       </c>
       <c r="H57" s="3">
-        <v>23500</v>
+        <v>375000</v>
       </c>
       <c r="I57" s="3">
-        <v>24900</v>
+        <v>572200</v>
       </c>
       <c r="J57" s="3">
-        <v>25200</v>
+        <v>1291200</v>
       </c>
       <c r="K57" s="3">
         <v>14000</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>191700</v>
+        <v>228000</v>
       </c>
       <c r="E58" s="3">
-        <v>50600</v>
+        <v>275000</v>
       </c>
       <c r="F58" s="3">
-        <v>8900</v>
+        <v>83000</v>
       </c>
       <c r="G58" s="3">
-        <v>21200</v>
+        <v>244000</v>
       </c>
       <c r="H58" s="3">
-        <v>11400</v>
+        <v>187000</v>
       </c>
       <c r="I58" s="3">
-        <v>14900</v>
+        <v>342700</v>
       </c>
       <c r="J58" s="3">
-        <v>9000</v>
+        <v>460500</v>
       </c>
       <c r="K58" s="3">
         <v>11900</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>78200</v>
+        <v>49000</v>
       </c>
       <c r="E59" s="3">
-        <v>26500</v>
+        <v>73000</v>
       </c>
       <c r="F59" s="3">
-        <v>9600</v>
+        <v>37000</v>
       </c>
       <c r="G59" s="3">
-        <v>9500</v>
+        <v>1065000</v>
       </c>
       <c r="H59" s="3">
-        <v>18200</v>
+        <v>155000</v>
       </c>
       <c r="I59" s="3">
-        <v>11600</v>
+        <v>130000</v>
       </c>
       <c r="J59" s="3">
-        <v>11800</v>
+        <v>421400</v>
       </c>
       <c r="K59" s="3">
         <v>7600</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>438500</v>
+        <v>521000</v>
       </c>
       <c r="E60" s="3">
-        <v>116200</v>
+        <v>631000</v>
       </c>
       <c r="F60" s="3">
-        <v>36500</v>
+        <v>342000</v>
       </c>
       <c r="G60" s="3">
-        <v>39200</v>
+        <v>1469000</v>
       </c>
       <c r="H60" s="3">
-        <v>53200</v>
+        <v>854000</v>
       </c>
       <c r="I60" s="3">
-        <v>51400</v>
+        <v>1184800</v>
       </c>
       <c r="J60" s="3">
-        <v>46000</v>
+        <v>2549400</v>
       </c>
       <c r="K60" s="3">
         <v>33400</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1040900</v>
+        <v>1238000</v>
       </c>
       <c r="E61" s="3">
-        <v>248800</v>
+        <v>1350000</v>
       </c>
       <c r="F61" s="3">
-        <v>146200</v>
+        <v>1368000</v>
       </c>
       <c r="G61" s="3">
-        <v>120000</v>
+        <v>1382000</v>
       </c>
       <c r="H61" s="3">
-        <v>109900</v>
+        <v>1776000</v>
       </c>
       <c r="I61" s="3">
-        <v>79800</v>
+        <v>1898300</v>
       </c>
       <c r="J61" s="3">
-        <v>57000</v>
+        <v>3076200</v>
       </c>
       <c r="K61" s="3">
         <v>17000</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>461700</v>
+        <v>237000</v>
       </c>
       <c r="E62" s="3">
-        <v>87900</v>
+        <v>337000</v>
       </c>
       <c r="F62" s="3">
-        <v>38400</v>
+        <v>336000</v>
       </c>
       <c r="G62" s="3">
-        <v>24500</v>
+        <v>252000</v>
       </c>
       <c r="H62" s="3">
-        <v>41000</v>
+        <v>244000</v>
       </c>
       <c r="I62" s="3">
-        <v>37300</v>
+        <v>352100</v>
       </c>
       <c r="J62" s="3">
-        <v>37900</v>
+        <v>812300</v>
       </c>
       <c r="K62" s="3">
         <v>19800</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1948400</v>
+        <v>2309000</v>
       </c>
       <c r="E66" s="3">
-        <v>454100</v>
+        <v>2458000</v>
       </c>
       <c r="F66" s="3">
-        <v>221800</v>
+        <v>2070000</v>
       </c>
       <c r="G66" s="3">
-        <v>302900</v>
+        <v>3121000</v>
       </c>
       <c r="H66" s="3">
-        <v>234600</v>
+        <v>3275000</v>
       </c>
       <c r="I66" s="3">
-        <v>187100</v>
+        <v>3881900</v>
       </c>
       <c r="J66" s="3">
-        <v>163000</v>
+        <v>7422800</v>
       </c>
       <c r="K66" s="3">
         <v>73500</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1430800</v>
+        <v>1686000</v>
       </c>
       <c r="E72" s="3">
-        <v>274000</v>
+        <v>1475000</v>
       </c>
       <c r="F72" s="3">
-        <v>107800</v>
+        <v>1000000</v>
       </c>
       <c r="G72" s="3">
-        <v>64500</v>
+        <v>728000</v>
       </c>
       <c r="H72" s="3">
-        <v>73400</v>
+        <v>1172000</v>
       </c>
       <c r="I72" s="3">
-        <v>26500</v>
+        <v>610100</v>
       </c>
       <c r="J72" s="3">
-        <v>26500</v>
+        <v>1359800</v>
       </c>
       <c r="K72" s="3">
         <v>4500</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2021500</v>
+        <v>2404000</v>
       </c>
       <c r="E76" s="3">
-        <v>419600</v>
+        <v>2277000</v>
       </c>
       <c r="F76" s="3">
-        <v>190800</v>
+        <v>1785000</v>
       </c>
       <c r="G76" s="3">
-        <v>125100</v>
+        <v>1428000</v>
       </c>
       <c r="H76" s="3">
-        <v>119500</v>
+        <v>1917000</v>
       </c>
       <c r="I76" s="3">
-        <v>59400</v>
+        <v>1368500</v>
       </c>
       <c r="J76" s="3">
-        <v>58700</v>
+        <v>3016300</v>
       </c>
       <c r="K76" s="3">
         <v>12300</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>35900</v>
+        <v>302000</v>
       </c>
       <c r="E81" s="3">
-        <v>67500</v>
+        <v>456000</v>
       </c>
       <c r="F81" s="3">
-        <v>28200</v>
+        <v>273000</v>
       </c>
       <c r="G81" s="3">
-        <v>-32700</v>
+        <v>-367000</v>
       </c>
       <c r="H81" s="3">
-        <v>34300</v>
+        <v>692000</v>
       </c>
       <c r="I81" s="3">
-        <v>8800</v>
+        <v>224000</v>
       </c>
       <c r="J81" s="3">
-        <v>11200</v>
+        <v>576700</v>
       </c>
       <c r="K81" s="3">
         <v>0</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>82700</v>
+        <v>267000</v>
       </c>
       <c r="E83" s="3">
-        <v>28800</v>
+        <v>212000</v>
       </c>
       <c r="F83" s="3">
-        <v>20500</v>
+        <v>205000</v>
       </c>
       <c r="G83" s="3">
-        <v>15100</v>
+        <v>200000</v>
       </c>
       <c r="H83" s="3">
-        <v>14500</v>
+        <v>180000</v>
       </c>
       <c r="I83" s="3">
-        <v>9200</v>
+        <v>159000</v>
       </c>
       <c r="J83" s="3">
-        <v>8000</v>
+        <v>410500</v>
       </c>
       <c r="K83" s="3">
         <v>2400</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>184200</v>
+        <v>575000</v>
       </c>
       <c r="E89" s="3">
-        <v>84400</v>
+        <v>619000</v>
       </c>
       <c r="F89" s="3">
-        <v>79400</v>
+        <v>729000</v>
       </c>
       <c r="G89" s="3">
-        <v>49200</v>
+        <v>693000</v>
       </c>
       <c r="H89" s="3">
-        <v>39200</v>
+        <v>802000</v>
       </c>
       <c r="I89" s="3">
-        <v>23800</v>
+        <v>610000</v>
       </c>
       <c r="J89" s="3">
-        <v>16600</v>
+        <v>888400</v>
       </c>
       <c r="K89" s="3">
         <v>6600</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-202000</v>
+        <v>-758000</v>
       </c>
       <c r="E91" s="3">
-        <v>-54000</v>
+        <v>-416000</v>
       </c>
       <c r="F91" s="3">
-        <v>-20300</v>
+        <v>-206000</v>
       </c>
       <c r="G91" s="3">
-        <v>-8700</v>
+        <v>-124000</v>
       </c>
       <c r="H91" s="3">
-        <v>-30000</v>
+        <v>-426000</v>
       </c>
       <c r="I91" s="3">
-        <v>-26400</v>
+        <v>-455000</v>
       </c>
       <c r="J91" s="3">
-        <v>-19000</v>
+        <v>-976800</v>
       </c>
       <c r="K91" s="3">
         <v>-6900</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-78400</v>
+        <v>-446000</v>
       </c>
       <c r="E94" s="3">
-        <v>-78100</v>
+        <v>-575000</v>
       </c>
       <c r="F94" s="3">
-        <v>-47600</v>
+        <v>-474000</v>
       </c>
       <c r="G94" s="3">
-        <v>-16200</v>
+        <v>-255000</v>
       </c>
       <c r="H94" s="3">
-        <v>-17900</v>
+        <v>-369000</v>
       </c>
       <c r="I94" s="3">
-        <v>800</v>
+        <v>19000</v>
       </c>
       <c r="J94" s="3">
-        <v>-33200</v>
+        <v>-1705700</v>
       </c>
       <c r="K94" s="3">
         <v>-12500</v>
@@ -4227,7 +4227,7 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-500</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
@@ -4236,16 +4236,16 @@
         <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-55200</v>
+        <v>-57000</v>
       </c>
       <c r="E100" s="3">
-        <v>-5300</v>
+        <v>-46000</v>
       </c>
       <c r="F100" s="3">
-        <v>-33100</v>
+        <v>-342000</v>
       </c>
       <c r="G100" s="3">
-        <v>-31200</v>
+        <v>-445000</v>
       </c>
       <c r="H100" s="3">
-        <v>-22000</v>
+        <v>-390000</v>
       </c>
       <c r="I100" s="3">
-        <v>-18400</v>
+        <v>-470000</v>
       </c>
       <c r="J100" s="3">
-        <v>14600</v>
+        <v>747900</v>
       </c>
       <c r="K100" s="3">
         <v>6500</v>
@@ -4452,25 +4452,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>73400</v>
+        <v>-7000</v>
       </c>
       <c r="E101" s="3">
-        <v>6700</v>
+        <v>-2000</v>
       </c>
       <c r="F101" s="3">
-        <v>600</v>
+        <v>4000</v>
       </c>
       <c r="G101" s="3">
-        <v>-3500</v>
+        <v>-25000</v>
       </c>
       <c r="H101" s="3">
-        <v>5300</v>
+        <v>-59000</v>
       </c>
       <c r="I101" s="3">
-        <v>2100</v>
+        <v>53000</v>
       </c>
       <c r="J101" s="3">
-        <v>500</v>
+        <v>27200</v>
       </c>
       <c r="K101" s="3">
         <v>400</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>124000</v>
+        <v>65000</v>
       </c>
       <c r="E102" s="3">
-        <v>7800</v>
+        <v>-4000</v>
       </c>
       <c r="F102" s="3">
-        <v>-600</v>
+        <v>-83000</v>
       </c>
       <c r="G102" s="3">
-        <v>-1700</v>
+        <v>-32000</v>
       </c>
       <c r="H102" s="3">
-        <v>4600</v>
+        <v>-16000</v>
       </c>
       <c r="I102" s="3">
-        <v>8200</v>
+        <v>212000</v>
       </c>
       <c r="J102" s="3">
-        <v>-1500</v>
+        <v>-42200</v>
       </c>
       <c r="K102" s="3">
         <v>1000</v>

--- a/AAII_Financials/Yearly/PAM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PAM_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
   <si>
     <t>PAM</t>
   </si>
@@ -656,207 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1732000</v>
+        <v>1680800</v>
       </c>
       <c r="E8" s="3">
-        <v>1829000</v>
+        <v>635400</v>
       </c>
       <c r="F8" s="3">
+        <v>1367300</v>
+      </c>
+      <c r="G8" s="3">
         <v>1508000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1073000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1340000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1436000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4379800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>27900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>30900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>61600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>65800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>110700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>136900</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1112000</v>
+        <v>1148400</v>
       </c>
       <c r="E9" s="3">
-        <v>1143000</v>
+        <v>396900</v>
       </c>
       <c r="F9" s="3">
+        <v>846600</v>
+      </c>
+      <c r="G9" s="3">
         <v>953000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>664000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>812000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>833000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3173300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>20300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>29400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>59800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>69100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>220500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>257900</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>620000</v>
+        <v>532400</v>
       </c>
       <c r="E10" s="3">
-        <v>686000</v>
+        <v>238600</v>
       </c>
       <c r="F10" s="3">
+        <v>520700</v>
+      </c>
+      <c r="G10" s="3">
         <v>555000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>409000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>528000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>603000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1206600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>7600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-3300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-109800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-120900</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -874,8 +886,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -900,11 +913,11 @@
       <c r="J12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="3">
         <v>100</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>8</v>
@@ -918,9 +931,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -963,99 +979,108 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>34000</v>
+        <v>0</v>
       </c>
       <c r="E14" s="3">
-        <v>16000</v>
+        <v>37200</v>
       </c>
       <c r="F14" s="3">
+        <v>4200</v>
+      </c>
+      <c r="G14" s="3">
         <v>-16000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>96000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>37000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-14000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>37200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>6200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>34200</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>267000</v>
+        <v>303800</v>
       </c>
       <c r="E15" s="3">
-        <v>212000</v>
+        <v>98100</v>
       </c>
       <c r="F15" s="3">
+        <v>154400</v>
+      </c>
+      <c r="G15" s="3">
         <v>205000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>204000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>184000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>165000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>413300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>600</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1095,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1341000</v>
+        <v>1473700</v>
       </c>
       <c r="E17" s="3">
-        <v>1322000</v>
+        <v>485300</v>
       </c>
       <c r="F17" s="3">
+        <v>983700</v>
+      </c>
+      <c r="G17" s="3">
         <v>1072000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>812000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>970000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1000000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3701700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>25700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>15200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>52800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>44500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>122000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>144700</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>391000</v>
+        <v>207100</v>
       </c>
       <c r="E18" s="3">
-        <v>507000</v>
+        <v>150100</v>
       </c>
       <c r="F18" s="3">
+        <v>383600</v>
+      </c>
+      <c r="G18" s="3">
         <v>436000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>261000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>370000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>436000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>678100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>15700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>8800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>21300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-11300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1179,233 +1211,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-547000</v>
+        <v>-339200</v>
       </c>
       <c r="E20" s="3">
-        <v>-274000</v>
+        <v>-194400</v>
       </c>
       <c r="F20" s="3">
+        <v>-238700</v>
+      </c>
+      <c r="G20" s="3">
         <v>-79000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-124000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-247000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>294000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-499600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>7500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>7100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-3000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>7000</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1205000</v>
+        <v>850000</v>
       </c>
       <c r="E21" s="3">
-        <v>993000</v>
+        <v>442500</v>
       </c>
       <c r="F21" s="3">
+        <v>776700</v>
+      </c>
+      <c r="G21" s="3">
         <v>720000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>589000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>801000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>307000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1591100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>26300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>20500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>22900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-7900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>9600</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>356000</v>
+        <v>160600</v>
       </c>
       <c r="E22" s="3">
-        <v>216000</v>
+        <v>127300</v>
       </c>
       <c r="F22" s="3">
+        <v>168200</v>
+      </c>
+      <c r="G22" s="3">
         <v>178000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>170000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>183000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>179000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>458700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>3400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>4000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>9600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>9300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>6500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>19200</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>623000</v>
+        <v>460400</v>
       </c>
       <c r="E23" s="3">
-        <v>581000</v>
+        <v>209300</v>
       </c>
       <c r="F23" s="3">
+        <v>475900</v>
+      </c>
+      <c r="G23" s="3">
         <v>390000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>159000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>473000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>59000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>809500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>19100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>6200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>9000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-20600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-20100</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>318000</v>
+        <v>-87400</v>
       </c>
       <c r="E24" s="3">
-        <v>124000</v>
+        <v>164000</v>
       </c>
       <c r="F24" s="3">
+        <v>109500</v>
+      </c>
+      <c r="G24" s="3">
         <v>77000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>35000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-130000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-32000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-52600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-1300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-2200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1448,99 +1496,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>305000</v>
+        <v>547800</v>
       </c>
       <c r="E26" s="3">
-        <v>457000</v>
+        <v>45400</v>
       </c>
       <c r="F26" s="3">
+        <v>366400</v>
+      </c>
+      <c r="G26" s="3">
         <v>313000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>124000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>603000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>91000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>862100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>16600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>9200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-18400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-19100</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>302000</v>
+        <v>547600</v>
       </c>
       <c r="E27" s="3">
-        <v>456000</v>
+        <v>42700</v>
       </c>
       <c r="F27" s="3">
+        <v>366200</v>
+      </c>
+      <c r="G27" s="3">
         <v>273000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-367000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>692000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>224000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>576800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>13200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>7400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-11300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3300</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1583,9 +1640,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1596,41 +1656,44 @@
         <v>0</v>
       </c>
       <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
         <v>-75000</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-592000</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>197000</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>196000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-101100</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>100</v>
       </c>
-      <c r="L29" s="3" t="s">
+      <c r="M29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>-1600</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>500</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1673,9 +1736,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1718,99 +1784,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>547000</v>
+        <v>339200</v>
       </c>
       <c r="E32" s="3">
-        <v>274000</v>
+        <v>194400</v>
       </c>
       <c r="F32" s="3">
+        <v>238700</v>
+      </c>
+      <c r="G32" s="3">
         <v>79000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>124000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>247000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-294000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>499600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-7500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-7100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>3000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>302000</v>
+        <v>547600</v>
       </c>
       <c r="E33" s="3">
-        <v>456000</v>
+        <v>42700</v>
       </c>
       <c r="F33" s="3">
+        <v>366200</v>
+      </c>
+      <c r="G33" s="3">
         <v>273000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-367000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>692000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>224000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>576700</v>
       </c>
-      <c r="K33" s="3">
-        <v>0</v>
-      </c>
       <c r="L33" s="3">
+        <v>0</v>
+      </c>
+      <c r="M33" s="3">
         <v>13200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>7400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-10700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>900</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,104 +1928,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>302000</v>
+        <v>547600</v>
       </c>
       <c r="E35" s="3">
-        <v>456000</v>
+        <v>42700</v>
       </c>
       <c r="F35" s="3">
+        <v>366200</v>
+      </c>
+      <c r="G35" s="3">
         <v>273000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-367000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>692000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>224000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>576700</v>
       </c>
-      <c r="K35" s="3">
-        <v>0</v>
-      </c>
       <c r="L35" s="3">
+        <v>0</v>
+      </c>
+      <c r="M35" s="3">
         <v>13200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>7400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-10700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>900</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1968,8 +2052,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1987,413 +2072,441 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>171000</v>
+        <v>738300</v>
       </c>
       <c r="E41" s="3">
+        <v>170700</v>
+      </c>
+      <c r="F41" s="3">
         <v>106000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>110000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>141000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>225000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>241600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>63000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>9000</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>664000</v>
+        <v>931400</v>
       </c>
       <c r="E42" s="3">
+        <v>663800</v>
+      </c>
+      <c r="F42" s="3">
         <v>594000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>463000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>350000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>419000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>441000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1154300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>4700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>17600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>10200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>13200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>5000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>9600</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>262000</v>
+        <v>355000</v>
       </c>
       <c r="E43" s="3">
+        <v>260000</v>
+      </c>
+      <c r="F43" s="3">
         <v>429000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>357000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>331000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>554000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>686900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1418300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>15500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>20600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>28200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>27900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>28700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>35300</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>205000</v>
+        <v>223200</v>
       </c>
       <c r="E44" s="3">
+        <v>205400</v>
+      </c>
+      <c r="F44" s="3">
         <v>173000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>155000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>116000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>153000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>137300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>227800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2600</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>29000</v>
+        <v>134300</v>
       </c>
       <c r="E45" s="3">
+        <v>35000</v>
+      </c>
+      <c r="F45" s="3">
         <v>27000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>30000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1475000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>9000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>15100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1071900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>7700</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1336000</v>
+        <v>2382200</v>
       </c>
       <c r="E46" s="3">
+        <v>1334800</v>
+      </c>
+      <c r="F46" s="3">
         <v>1343000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1125000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2417000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1362000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1523500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3940800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>25700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>41800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>43700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>43900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>35200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>49700</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>707000</v>
+        <v>1021200</v>
       </c>
       <c r="E47" s="3">
+        <v>706300</v>
+      </c>
+      <c r="F47" s="3">
         <v>1031000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>908000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>660000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>540000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>418500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>649500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>10800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>17900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>22600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>13900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>25600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>41700</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2501000</v>
+        <v>2582600</v>
       </c>
       <c r="E48" s="3">
+        <v>2500300</v>
+      </c>
+      <c r="F48" s="3">
         <v>2130000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1619000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1606000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3505000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3301000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5901000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>45600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>62500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>91500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>85200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>199100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>329000</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>96000</v>
+        <v>96200</v>
       </c>
       <c r="E49" s="3">
+        <v>96400</v>
+      </c>
+      <c r="F49" s="3">
         <v>138000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>38000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>41000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>151000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>161500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>339400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>11100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>59600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>91000</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,9 +2549,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2481,54 +2597,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>82000</v>
+        <v>112800</v>
       </c>
       <c r="E52" s="3">
+        <v>83600</v>
+      </c>
+      <c r="F52" s="3">
         <v>64000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>87000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>58000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>90000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>180000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>229200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>200</v>
-      </c>
-      <c r="M52" s="3">
-        <v>900</v>
       </c>
       <c r="N52" s="3">
         <v>900</v>
       </c>
       <c r="O52" s="3">
+        <v>900</v>
+      </c>
+      <c r="P52" s="3">
         <v>12300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>81600</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2571,54 +2693,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>4722000</v>
+        <v>6352000</v>
       </c>
       <c r="E54" s="3">
+        <v>4721400</v>
+      </c>
+      <c r="F54" s="3">
         <v>4742000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3861000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4890000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5684000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5679500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>11389400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>85800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>125600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>167300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>155000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>187100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>316500</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2636,8 +2764,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2655,278 +2784,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>201000</v>
+        <v>219400</v>
       </c>
       <c r="E57" s="3">
+        <v>200600</v>
+      </c>
+      <c r="F57" s="3">
         <v>212000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>169000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>97000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>375000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>572200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1291200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>14000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>28500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>45000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>38100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>52600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>25300</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>228000</v>
+        <v>709800</v>
       </c>
       <c r="E58" s="3">
+        <v>227900</v>
+      </c>
+      <c r="F58" s="3">
         <v>275000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>83000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>244000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>187000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>342700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>460500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>11900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>5600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>7800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>9300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>13100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>47000</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>49000</v>
+        <v>303400</v>
       </c>
       <c r="E59" s="3">
+        <v>50000</v>
+      </c>
+      <c r="F59" s="3">
         <v>73000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>37000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1065000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>155000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>130000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>421400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>10500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>15200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>24200</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>521000</v>
+        <v>1303000</v>
       </c>
       <c r="E60" s="3">
+        <v>521600</v>
+      </c>
+      <c r="F60" s="3">
         <v>631000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>342000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1469000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>854000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1184800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2549400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>33400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>41300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>63300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>56900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>53000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>66100</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1385600</v>
+      </c>
+      <c r="E61" s="3">
         <v>1238000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1350000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1368000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1382000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1776000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1898300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3076200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>17000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>28800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>37600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>36100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>36700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>65100</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>237000</v>
+        <v>286200</v>
       </c>
       <c r="E62" s="3">
+        <v>235100</v>
+      </c>
+      <c r="F62" s="3">
         <v>337000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>336000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>252000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>244000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>352100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>812300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>19800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>19400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>31200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>26500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>90700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>73600</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2969,9 +3117,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3014,9 +3165,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3059,54 +3213,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>2309000</v>
+        <v>3053900</v>
       </c>
       <c r="E66" s="3">
+        <v>2308600</v>
+      </c>
+      <c r="F66" s="3">
         <v>2458000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2070000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3121000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3275000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3881900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7422800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>73500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>95500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>138300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>129100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>157300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>252600</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3124,8 +3284,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3168,9 +3329,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3213,9 +3377,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3258,9 +3425,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3303,54 +3473,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1686000</v>
+        <v>2448000</v>
       </c>
       <c r="E72" s="3">
+        <v>1701700</v>
+      </c>
+      <c r="F72" s="3">
         <v>1475000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1000000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>728000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1172000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>610100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1359800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>17600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>12800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>6700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-8600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-10400</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3393,9 +3569,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3438,9 +3617,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3483,54 +3665,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2404000</v>
+        <v>3289200</v>
       </c>
       <c r="E76" s="3">
+        <v>2404200</v>
+      </c>
+      <c r="F76" s="3">
         <v>2277000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1785000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1428000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1917000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1368500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3016300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>12300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>30100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>29000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>25900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>29800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>63900</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3573,104 +3761,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>302000</v>
+        <v>547600</v>
       </c>
       <c r="E81" s="3">
-        <v>456000</v>
+        <v>42700</v>
       </c>
       <c r="F81" s="3">
+        <v>366200</v>
+      </c>
+      <c r="G81" s="3">
         <v>273000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-367000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>692000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>224000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>576700</v>
       </c>
-      <c r="K81" s="3">
-        <v>0</v>
-      </c>
       <c r="L81" s="3">
+        <v>0</v>
+      </c>
+      <c r="M81" s="3">
         <v>13200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>7400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-10700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>900</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3688,53 +3885,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>267000</v>
+        <v>302400</v>
       </c>
       <c r="E83" s="3">
-        <v>212000</v>
+        <v>96600</v>
       </c>
       <c r="F83" s="3">
+        <v>155500</v>
+      </c>
+      <c r="G83" s="3">
         <v>205000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>200000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>180000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>159000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>410500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3100</v>
-      </c>
-      <c r="M83" s="3">
-        <v>4600</v>
       </c>
       <c r="N83" s="3">
         <v>4600</v>
       </c>
       <c r="O83" s="3">
+        <v>4600</v>
+      </c>
+      <c r="P83" s="3">
         <v>6200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>10200</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3777,9 +3978,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3822,9 +4026,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3867,9 +4074,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3912,9 +4122,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3957,54 +4170,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>575000</v>
+        <v>370500</v>
       </c>
       <c r="E89" s="3">
-        <v>619000</v>
+        <v>219100</v>
       </c>
       <c r="F89" s="3">
+        <v>458400</v>
+      </c>
+      <c r="G89" s="3">
         <v>729000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>693000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>802000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>610000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>888400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>6600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>18800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>25500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>22200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>19800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>29800</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4022,53 +4241,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-758000</v>
+        <v>-382900</v>
       </c>
       <c r="E91" s="3">
-        <v>-416000</v>
+        <v>-240300</v>
       </c>
       <c r="F91" s="3">
+        <v>-293100</v>
+      </c>
+      <c r="G91" s="3">
         <v>-206000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-124000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-426000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-455000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-976800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-20700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-23100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-14800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-11300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-42800</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4111,9 +4334,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4156,54 +4382,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-446000</v>
+        <v>-295500</v>
       </c>
       <c r="E94" s="3">
-        <v>-575000</v>
+        <v>-93200</v>
       </c>
       <c r="F94" s="3">
+        <v>-423700</v>
+      </c>
+      <c r="G94" s="3">
         <v>-474000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-255000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-369000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>19000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1705700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-12500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-30700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-24500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-19400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-14900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-44900</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4221,8 +4453,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4230,10 +4463,10 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
@@ -4251,23 +4484,26 @@
         <v>0</v>
       </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-200</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-500</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4310,9 +4546,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4355,9 +4594,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4400,142 +4642,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-57000</v>
+        <v>455000</v>
       </c>
       <c r="E100" s="3">
-        <v>-46000</v>
+        <v>-65700</v>
       </c>
       <c r="F100" s="3">
+        <v>-28600</v>
+      </c>
+      <c r="G100" s="3">
         <v>-342000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-445000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-390000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-470000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>747900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>6500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>12300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-9000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>10300</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-7000</v>
+        <v>74500</v>
       </c>
       <c r="E101" s="3">
-        <v>-2000</v>
+        <v>87300</v>
       </c>
       <c r="F101" s="3">
+        <v>36100</v>
+      </c>
+      <c r="G101" s="3">
         <v>4000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-25000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-59000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>53000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>27200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>2700</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>65000</v>
+        <v>604500</v>
       </c>
       <c r="E102" s="3">
-        <v>-4000</v>
+        <v>147500</v>
       </c>
       <c r="F102" s="3">
+        <v>42200</v>
+      </c>
+      <c r="G102" s="3">
         <v>-83000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-32000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-16000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>212000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-42200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/PAM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PAM_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="92">
   <si>
     <t>PAM</t>
   </si>
@@ -729,13 +729,13 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1680800</v>
+        <v>1876000</v>
       </c>
       <c r="E8" s="3">
-        <v>635400</v>
+        <v>1732000</v>
       </c>
       <c r="F8" s="3">
-        <v>1367300</v>
+        <v>1829000</v>
       </c>
       <c r="G8" s="3">
         <v>1508000</v>
@@ -777,13 +777,13 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1148400</v>
+        <v>1282000</v>
       </c>
       <c r="E9" s="3">
-        <v>396900</v>
+        <v>1112000</v>
       </c>
       <c r="F9" s="3">
-        <v>846600</v>
+        <v>1141000</v>
       </c>
       <c r="G9" s="3">
         <v>953000</v>
@@ -825,13 +825,13 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>532400</v>
+        <v>594000</v>
       </c>
       <c r="E10" s="3">
-        <v>238600</v>
+        <v>620000</v>
       </c>
       <c r="F10" s="3">
-        <v>520700</v>
+        <v>688000</v>
       </c>
       <c r="G10" s="3">
         <v>555000</v>
@@ -989,13 +989,13 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="E14" s="3">
-        <v>37200</v>
+        <v>34000</v>
       </c>
       <c r="F14" s="3">
-        <v>4200</v>
+        <v>18000</v>
       </c>
       <c r="G14" s="3">
         <v>-16000</v>
@@ -1037,13 +1037,13 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>303800</v>
+        <v>340000</v>
       </c>
       <c r="E15" s="3">
-        <v>98100</v>
+        <v>266000</v>
       </c>
       <c r="F15" s="3">
-        <v>154400</v>
+        <v>209000</v>
       </c>
       <c r="G15" s="3">
         <v>205000</v>
@@ -1102,13 +1102,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1473700</v>
+        <v>1644000</v>
       </c>
       <c r="E17" s="3">
-        <v>485300</v>
+        <v>1341000</v>
       </c>
       <c r="F17" s="3">
-        <v>983700</v>
+        <v>1320000</v>
       </c>
       <c r="G17" s="3">
         <v>1072000</v>
@@ -1150,13 +1150,13 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>207100</v>
+        <v>232000</v>
       </c>
       <c r="E18" s="3">
-        <v>150100</v>
+        <v>391000</v>
       </c>
       <c r="F18" s="3">
-        <v>383600</v>
+        <v>509000</v>
       </c>
       <c r="G18" s="3">
         <v>436000</v>
@@ -1218,13 +1218,13 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-339200</v>
+        <v>-362000</v>
       </c>
       <c r="E20" s="3">
-        <v>-194400</v>
+        <v>-547000</v>
       </c>
       <c r="F20" s="3">
-        <v>-238700</v>
+        <v>-274000</v>
       </c>
       <c r="G20" s="3">
         <v>-79000</v>
@@ -1266,13 +1266,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>850000</v>
+        <v>934000</v>
       </c>
       <c r="E21" s="3">
-        <v>442500</v>
+        <v>1204000</v>
       </c>
       <c r="F21" s="3">
-        <v>776700</v>
+        <v>992000</v>
       </c>
       <c r="G21" s="3">
         <v>720000</v>
@@ -1314,13 +1314,13 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>160600</v>
+        <v>180000</v>
       </c>
       <c r="E22" s="3">
-        <v>127300</v>
+        <v>356000</v>
       </c>
       <c r="F22" s="3">
-        <v>168200</v>
+        <v>216000</v>
       </c>
       <c r="G22" s="3">
         <v>178000</v>
@@ -1362,13 +1362,13 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>460400</v>
+        <v>498000</v>
       </c>
       <c r="E23" s="3">
-        <v>209300</v>
+        <v>623000</v>
       </c>
       <c r="F23" s="3">
-        <v>475900</v>
+        <v>581000</v>
       </c>
       <c r="G23" s="3">
         <v>390000</v>
@@ -1410,13 +1410,13 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-87400</v>
+        <v>-121000</v>
       </c>
       <c r="E24" s="3">
-        <v>164000</v>
+        <v>318000</v>
       </c>
       <c r="F24" s="3">
-        <v>109500</v>
+        <v>124000</v>
       </c>
       <c r="G24" s="3">
         <v>77000</v>
@@ -1506,13 +1506,13 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>547800</v>
+        <v>619000</v>
       </c>
       <c r="E26" s="3">
-        <v>45400</v>
+        <v>305000</v>
       </c>
       <c r="F26" s="3">
-        <v>366400</v>
+        <v>457000</v>
       </c>
       <c r="G26" s="3">
         <v>313000</v>
@@ -1554,13 +1554,13 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>547600</v>
+        <v>619000</v>
       </c>
       <c r="E27" s="3">
-        <v>42700</v>
+        <v>302000</v>
       </c>
       <c r="F27" s="3">
-        <v>366200</v>
+        <v>456000</v>
       </c>
       <c r="G27" s="3">
         <v>273000</v>
@@ -1794,13 +1794,13 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>339200</v>
+        <v>362000</v>
       </c>
       <c r="E32" s="3">
-        <v>194400</v>
+        <v>547000</v>
       </c>
       <c r="F32" s="3">
-        <v>238700</v>
+        <v>274000</v>
       </c>
       <c r="G32" s="3">
         <v>79000</v>
@@ -1842,13 +1842,13 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>547600</v>
+        <v>619000</v>
       </c>
       <c r="E33" s="3">
-        <v>42700</v>
+        <v>302000</v>
       </c>
       <c r="F33" s="3">
-        <v>366200</v>
+        <v>456000</v>
       </c>
       <c r="G33" s="3">
         <v>273000</v>
@@ -1938,13 +1938,13 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>547600</v>
+        <v>619000</v>
       </c>
       <c r="E35" s="3">
-        <v>42700</v>
+        <v>302000</v>
       </c>
       <c r="F35" s="3">
-        <v>366200</v>
+        <v>456000</v>
       </c>
       <c r="G35" s="3">
         <v>273000</v>
@@ -2079,10 +2079,10 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>738300</v>
+        <v>738000</v>
       </c>
       <c r="E41" s="3">
-        <v>170700</v>
+        <v>171000</v>
       </c>
       <c r="F41" s="3">
         <v>106000</v>
@@ -2127,10 +2127,10 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>931400</v>
+        <v>930000</v>
       </c>
       <c r="E42" s="3">
-        <v>663800</v>
+        <v>664000</v>
       </c>
       <c r="F42" s="3">
         <v>594000</v>
@@ -2178,7 +2178,7 @@
         <v>355000</v>
       </c>
       <c r="E43" s="3">
-        <v>260000</v>
+        <v>262000</v>
       </c>
       <c r="F43" s="3">
         <v>429000</v>
@@ -2223,10 +2223,10 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>223200</v>
+        <v>223000</v>
       </c>
       <c r="E44" s="3">
-        <v>205400</v>
+        <v>205000</v>
       </c>
       <c r="F44" s="3">
         <v>173000</v>
@@ -2271,10 +2271,10 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>134300</v>
+        <v>131000</v>
       </c>
       <c r="E45" s="3">
-        <v>35000</v>
+        <v>29000</v>
       </c>
       <c r="F45" s="3">
         <v>27000</v>
@@ -2319,10 +2319,10 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>2382200</v>
+        <v>2380000</v>
       </c>
       <c r="E46" s="3">
-        <v>1334800</v>
+        <v>1336000</v>
       </c>
       <c r="F46" s="3">
         <v>1343000</v>
@@ -2367,10 +2367,10 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1021200</v>
+        <v>1020000</v>
       </c>
       <c r="E47" s="3">
-        <v>706300</v>
+        <v>707000</v>
       </c>
       <c r="F47" s="3">
         <v>1031000</v>
@@ -2415,10 +2415,10 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2582600</v>
+        <v>2580000</v>
       </c>
       <c r="E48" s="3">
-        <v>2500300</v>
+        <v>2501000</v>
       </c>
       <c r="F48" s="3">
         <v>2130000</v>
@@ -2463,10 +2463,10 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>96200</v>
+        <v>95000</v>
       </c>
       <c r="E49" s="3">
-        <v>96400</v>
+        <v>96000</v>
       </c>
       <c r="F49" s="3">
         <v>138000</v>
@@ -2607,10 +2607,10 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>112800</v>
+        <v>113000</v>
       </c>
       <c r="E52" s="3">
-        <v>83600</v>
+        <v>82000</v>
       </c>
       <c r="F52" s="3">
         <v>64000</v>
@@ -2703,10 +2703,10 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>6352000</v>
+        <v>6345000</v>
       </c>
       <c r="E54" s="3">
-        <v>4721400</v>
+        <v>4722000</v>
       </c>
       <c r="F54" s="3">
         <v>4742000</v>
@@ -2791,10 +2791,10 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>219400</v>
+        <v>219000</v>
       </c>
       <c r="E57" s="3">
-        <v>200600</v>
+        <v>201000</v>
       </c>
       <c r="F57" s="3">
         <v>212000</v>
@@ -2839,10 +2839,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>709800</v>
+        <v>710000</v>
       </c>
       <c r="E58" s="3">
-        <v>227900</v>
+        <v>228000</v>
       </c>
       <c r="F58" s="3">
         <v>275000</v>
@@ -2887,10 +2887,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>303400</v>
+        <v>302000</v>
       </c>
       <c r="E59" s="3">
-        <v>50000</v>
+        <v>49000</v>
       </c>
       <c r="F59" s="3">
         <v>73000</v>
@@ -2935,10 +2935,10 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1303000</v>
+        <v>1302000</v>
       </c>
       <c r="E60" s="3">
-        <v>521600</v>
+        <v>521000</v>
       </c>
       <c r="F60" s="3">
         <v>631000</v>
@@ -2983,7 +2983,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1385600</v>
+        <v>1384000</v>
       </c>
       <c r="E61" s="3">
         <v>1238000</v>
@@ -3031,10 +3031,10 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>286200</v>
+        <v>285000</v>
       </c>
       <c r="E62" s="3">
-        <v>235100</v>
+        <v>237000</v>
       </c>
       <c r="F62" s="3">
         <v>337000</v>
@@ -3223,10 +3223,10 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>3053900</v>
+        <v>3050000</v>
       </c>
       <c r="E66" s="3">
-        <v>2308600</v>
+        <v>2309000</v>
       </c>
       <c r="F66" s="3">
         <v>2458000</v>
@@ -3483,10 +3483,10 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2448000</v>
+        <v>2430000</v>
       </c>
       <c r="E72" s="3">
-        <v>1701700</v>
+        <v>1686000</v>
       </c>
       <c r="F72" s="3">
         <v>1475000</v>
@@ -3675,10 +3675,10 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>3289200</v>
+        <v>3286000</v>
       </c>
       <c r="E76" s="3">
-        <v>2404200</v>
+        <v>2404000</v>
       </c>
       <c r="F76" s="3">
         <v>2277000</v>
@@ -3824,13 +3824,13 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>547600</v>
+        <v>619000</v>
       </c>
       <c r="E81" s="3">
-        <v>42700</v>
+        <v>302000</v>
       </c>
       <c r="F81" s="3">
-        <v>366200</v>
+        <v>456000</v>
       </c>
       <c r="G81" s="3">
         <v>273000</v>
@@ -3892,13 +3892,13 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>302400</v>
+        <v>338000</v>
       </c>
       <c r="E83" s="3">
-        <v>96600</v>
+        <v>262000</v>
       </c>
       <c r="F83" s="3">
-        <v>155500</v>
+        <v>211000</v>
       </c>
       <c r="G83" s="3">
         <v>205000</v>
@@ -4180,13 +4180,13 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>370500</v>
+        <v>435000</v>
       </c>
       <c r="E89" s="3">
-        <v>219100</v>
+        <v>575000</v>
       </c>
       <c r="F89" s="3">
-        <v>458400</v>
+        <v>619000</v>
       </c>
       <c r="G89" s="3">
         <v>729000</v>
@@ -4248,13 +4248,13 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-382900</v>
+        <v>-447000</v>
       </c>
       <c r="E91" s="3">
-        <v>-240300</v>
+        <v>-758000</v>
       </c>
       <c r="F91" s="3">
-        <v>-293100</v>
+        <v>-416000</v>
       </c>
       <c r="G91" s="3">
         <v>-206000</v>
@@ -4392,13 +4392,13 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-295500</v>
+        <v>-344000</v>
       </c>
       <c r="E94" s="3">
-        <v>-93200</v>
+        <v>-446000</v>
       </c>
       <c r="F94" s="3">
-        <v>-423700</v>
+        <v>-575000</v>
       </c>
       <c r="G94" s="3">
         <v>-474000</v>
@@ -4463,10 +4463,10 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="F96" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
@@ -4652,13 +4652,13 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>455000</v>
+        <v>476000</v>
       </c>
       <c r="E100" s="3">
-        <v>-65700</v>
+        <v>-57000</v>
       </c>
       <c r="F100" s="3">
-        <v>-28600</v>
+        <v>-46000</v>
       </c>
       <c r="G100" s="3">
         <v>-342000</v>
@@ -4699,14 +4699,14 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>74500</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E101" s="3">
-        <v>87300</v>
+        <v>-7000</v>
       </c>
       <c r="F101" s="3">
-        <v>36100</v>
+        <v>-2000</v>
       </c>
       <c r="G101" s="3">
         <v>4000</v>
@@ -4748,13 +4748,13 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>604500</v>
+        <v>567000</v>
       </c>
       <c r="E102" s="3">
-        <v>147500</v>
+        <v>65000</v>
       </c>
       <c r="F102" s="3">
-        <v>42200</v>
+        <v>-4000</v>
       </c>
       <c r="G102" s="3">
         <v>-83000</v>

--- a/AAII_Financials/Yearly/PAM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PAM_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
   <si>
     <t>PAM</t>
   </si>
@@ -656,219 +656,231 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1998000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1876000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1732000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1829000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1508000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1073000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1340000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1436000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4379800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>27900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>30900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>61600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>65800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>110700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>136900</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1372400</v>
+      </c>
+      <c r="E9" s="3">
         <v>1282000</v>
       </c>
-      <c r="E9" s="3">
-        <v>1112000</v>
-      </c>
       <c r="F9" s="3">
+        <v>1109000</v>
+      </c>
+      <c r="G9" s="3">
         <v>1141000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>953000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>664000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>812000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>833000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3173300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>20300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>29400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>59800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>69100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>220500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>257900</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>625600</v>
+      </c>
+      <c r="E10" s="3">
         <v>594000</v>
       </c>
-      <c r="E10" s="3">
-        <v>620000</v>
-      </c>
       <c r="F10" s="3">
+        <v>623000</v>
+      </c>
+      <c r="G10" s="3">
         <v>688000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>555000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>409000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>528000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>603000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1206600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>7600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-3300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-109800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-120900</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -887,8 +899,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -916,11 +929,11 @@
       <c r="K12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="3">
         <v>100</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>8</v>
@@ -934,9 +947,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -982,105 +998,114 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-47400</v>
+      </c>
+      <c r="E14" s="3">
         <v>-2000</v>
       </c>
-      <c r="E14" s="3">
-        <v>34000</v>
-      </c>
       <c r="F14" s="3">
+        <v>37000</v>
+      </c>
+      <c r="G14" s="3">
         <v>18000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-16000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>96000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>37000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-14000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>37200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>6200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>34200</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>397000</v>
+      </c>
+      <c r="E15" s="3">
         <v>340000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>266000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>209000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>205000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>204000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>184000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>165000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>413300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>600</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,104 +1121,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1696400</v>
+      </c>
+      <c r="E17" s="3">
         <v>1644000</v>
       </c>
-      <c r="E17" s="3">
-        <v>1341000</v>
-      </c>
       <c r="F17" s="3">
+        <v>1338000</v>
+      </c>
+      <c r="G17" s="3">
         <v>1320000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1072000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>812000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>970000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1000000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3701700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>25700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>15200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>52800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>44500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>122000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>144700</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>301600</v>
+      </c>
+      <c r="E18" s="3">
         <v>232000</v>
       </c>
-      <c r="E18" s="3">
-        <v>391000</v>
-      </c>
       <c r="F18" s="3">
+        <v>394000</v>
+      </c>
+      <c r="G18" s="3">
         <v>509000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>436000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>261000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>370000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>436000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>678100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>15700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>8800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>21300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-11300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-7800</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1212,248 +1244,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-363000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-362000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-547000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-274000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-79000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-124000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-247000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>294000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-499600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>7500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>7100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-3000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>7000</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1061600</v>
+      </c>
+      <c r="E21" s="3">
         <v>934000</v>
       </c>
-      <c r="E21" s="3">
-        <v>1204000</v>
-      </c>
       <c r="F21" s="3">
+        <v>1207000</v>
+      </c>
+      <c r="G21" s="3">
         <v>992000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>720000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>589000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>801000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>307000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1591100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>26300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>20500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>22900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>9600</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>189000</v>
+      </c>
+      <c r="E22" s="3">
         <v>180000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>356000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>216000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>178000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>170000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>183000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>179000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>458700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>3400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>4000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>9600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>9300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>6500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>19200</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>582000</v>
+      </c>
+      <c r="E23" s="3">
         <v>498000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>623000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>581000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>390000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>159000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>473000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>59000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>809500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>19100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>6200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>9000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-20600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-20100</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>204000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-121000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>318000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>124000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>77000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>35000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-130000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-32000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-52600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-1300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-1000</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1499,105 +1547,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>378000</v>
+      </c>
+      <c r="E26" s="3">
         <v>619000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>305000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>457000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>313000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>124000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>603000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>91000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>862100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>16600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>9200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-18400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-19100</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>377000</v>
+      </c>
+      <c r="E27" s="3">
         <v>619000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>302000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>456000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>273000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-367000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>692000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>224000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>576800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>13200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>7400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-11300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3300</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1643,9 +1700,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1659,41 +1719,44 @@
         <v>0</v>
       </c>
       <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>-75000</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-592000</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>197000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>196000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-101100</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>100</v>
       </c>
-      <c r="M29" s="3" t="s">
+      <c r="N29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>-1600</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>500</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-2400</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1739,9 +1802,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1787,105 +1853,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>363000</v>
+      </c>
+      <c r="E32" s="3">
         <v>362000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>547000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>274000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>79000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>124000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>247000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-294000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>499600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-7500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-7100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>3000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-7000</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>377000</v>
+      </c>
+      <c r="E33" s="3">
         <v>619000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>302000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>456000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>273000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-367000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>692000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>224000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>576700</v>
       </c>
-      <c r="L33" s="3">
-        <v>0</v>
-      </c>
       <c r="M33" s="3">
+        <v>0</v>
+      </c>
+      <c r="N33" s="3">
         <v>13200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>7400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>3500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-10700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>900</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1931,110 +2006,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>377000</v>
+      </c>
+      <c r="E35" s="3">
         <v>619000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>302000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>456000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>273000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-367000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>692000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>224000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>576700</v>
       </c>
-      <c r="L35" s="3">
-        <v>0</v>
-      </c>
       <c r="M35" s="3">
+        <v>0</v>
+      </c>
+      <c r="N35" s="3">
         <v>13200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>7400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>3500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-10700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>900</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2053,8 +2137,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2073,440 +2158,468 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>725000</v>
+      </c>
+      <c r="E41" s="3">
         <v>738000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>171000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>106000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>110000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>141000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>225000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>241600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>63000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>9000</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>366000</v>
+      </c>
+      <c r="E42" s="3">
         <v>930000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>664000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>594000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>463000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>350000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>419000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>441000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1154300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>4700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>17600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>10200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>13200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>5000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>9600</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>454000</v>
+      </c>
+      <c r="E43" s="3">
         <v>355000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>262000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>429000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>357000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>331000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>554000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>686900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1418300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>15500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>20600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>28200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>27900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>28700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>35300</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>231000</v>
+      </c>
+      <c r="E44" s="3">
         <v>223000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>205000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>173000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>155000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>116000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>153000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>137300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>227800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2600</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>194000</v>
+      </c>
+      <c r="E45" s="3">
         <v>131000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>29000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>27000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>30000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1475000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>9000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>15100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1071900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>7700</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1988000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2380000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1336000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1343000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1125000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2417000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1362000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1523500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3940800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>25700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>41800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>43700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>43900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>35200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>49700</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1092000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1020000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>707000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1031000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>908000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>660000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>540000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>418500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>649500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>10800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>17900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>22600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>13900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>25600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>41700</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2580000</v>
+        <v>3339000</v>
       </c>
       <c r="E48" s="3">
+        <v>2618000</v>
+      </c>
+      <c r="F48" s="3">
         <v>2501000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2130000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1619000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1606000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3505000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3301000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5901000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>45600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>62500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>91500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>85200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>199100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>329000</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>89000</v>
+      </c>
+      <c r="E49" s="3">
         <v>95000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>96000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>138000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>38000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>41000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>151000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>161500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>339400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>11100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>59600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>91000</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2552,9 +2665,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2600,57 +2716,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>113000</v>
+        <v>43000</v>
       </c>
       <c r="E52" s="3">
+        <v>75000</v>
+      </c>
+      <c r="F52" s="3">
         <v>82000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>64000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>87000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>58000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>90000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>180000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>229200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>200</v>
-      </c>
-      <c r="N52" s="3">
-        <v>900</v>
       </c>
       <c r="O52" s="3">
         <v>900</v>
       </c>
       <c r="P52" s="3">
+        <v>900</v>
+      </c>
+      <c r="Q52" s="3">
         <v>12300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>81600</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2696,57 +2818,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6594000</v>
+      </c>
+      <c r="E54" s="3">
         <v>6345000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4722000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4742000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3861000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4890000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5684000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5679500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>11389400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>85800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>125600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>167300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>155000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>187100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>316500</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2765,8 +2893,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2785,296 +2914,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>343000</v>
+      </c>
+      <c r="E57" s="3">
         <v>219000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>201000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>212000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>169000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>97000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>375000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>572200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1291200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>14000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>28500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>45000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>38100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>52600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>25300</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>69000</v>
+      </c>
+      <c r="E58" s="3">
         <v>710000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>228000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>275000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>83000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>244000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>187000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>342700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>460500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>11900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>7800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>9300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>13100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>47000</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>133000</v>
+      </c>
+      <c r="E59" s="3">
         <v>302000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>49000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>73000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>37000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1065000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>155000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>130000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>421400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>9500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>15200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>24200</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>639000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1302000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>521000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>631000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>342000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1469000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>854000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1184800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2549400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>33400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>41300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>63300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>56900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>53000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>66100</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1859000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1384000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1238000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1350000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1368000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1382000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1776000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1898300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3076200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>17000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>28800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>37600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>36100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>36700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>65100</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>409000</v>
+      </c>
+      <c r="E62" s="3">
         <v>285000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>237000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>337000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>336000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>252000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>244000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>352100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>812300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>19800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>19400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>31200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>26500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>90700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>73600</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3120,9 +3268,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3168,9 +3319,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3216,57 +3370,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2989000</v>
+      </c>
+      <c r="E66" s="3">
         <v>3050000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2309000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2458000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2070000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3121000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3275000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3881900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7422800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>73500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>95500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>138300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>129100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>157300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>252600</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3285,8 +3445,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3332,9 +3493,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3380,9 +3544,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3428,9 +3595,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3476,57 +3646,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2782000</v>
+      </c>
+      <c r="E72" s="3">
         <v>2430000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1686000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1475000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1000000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>728000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1172000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>610100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1359800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>17600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>12800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>6700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-8600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-10400</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3572,9 +3748,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3620,9 +3799,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3668,57 +3850,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3596000</v>
+      </c>
+      <c r="E76" s="3">
         <v>3286000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2404000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2277000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1785000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1428000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1917000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1368500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3016300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>12300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>30100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>29000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>25900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>29800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>63900</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3764,110 +3952,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>377000</v>
+      </c>
+      <c r="E81" s="3">
         <v>619000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>302000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>456000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>273000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-367000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>692000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>224000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>576700</v>
       </c>
-      <c r="L81" s="3">
-        <v>0</v>
-      </c>
       <c r="M81" s="3">
+        <v>0</v>
+      </c>
+      <c r="N81" s="3">
         <v>13200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>7400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>3500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-10700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>900</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3886,56 +4083,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>410000</v>
+      </c>
+      <c r="E83" s="3">
         <v>338000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>262000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>211000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>205000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>200000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>180000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>159000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>410500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3100</v>
-      </c>
-      <c r="N83" s="3">
-        <v>4600</v>
       </c>
       <c r="O83" s="3">
         <v>4600</v>
       </c>
       <c r="P83" s="3">
+        <v>4600</v>
+      </c>
+      <c r="Q83" s="3">
         <v>6200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>10200</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3981,9 +4182,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4029,9 +4233,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4077,9 +4284,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4125,9 +4335,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4173,57 +4386,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>778000</v>
+      </c>
+      <c r="E89" s="3">
         <v>435000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>575000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>619000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>729000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>693000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>802000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>610000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>888400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>6600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>18800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>25500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>22200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>19800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>29800</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4242,56 +4461,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-993000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-447000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-758000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-416000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-206000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-124000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-426000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-455000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-976800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-20700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-23100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-14800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-11300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-42800</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4337,9 +4560,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4385,57 +4611,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-401000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-344000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-446000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-575000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-474000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-255000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-369000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>19000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1705700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-12500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-30700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-24500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-19400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-14900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-44900</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4454,20 +4686,21 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>1000</v>
       </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
       <c r="G96" s="3">
         <v>0</v>
       </c>
@@ -4487,23 +4720,26 @@
         <v>0</v>
       </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-200</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-500</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4549,9 +4785,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4597,9 +4836,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4645,151 +4887,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-390000</v>
+      </c>
+      <c r="E100" s="3">
         <v>476000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-57000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-46000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-342000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-445000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-390000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-470000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>747900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>6500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>12300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>10300</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E101" s="3">
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3">
         <v>-7000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-2000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>4000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-25000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-59000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>53000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>27200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>2700</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E102" s="3">
         <v>567000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>65000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-83000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-32000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-16000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>212000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-42200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2100</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
